--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F897CB7-53D5-4F1C-BE4C-F48006164CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0910DFD-BBE2-466F-ABC6-D09555C637AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="213">
   <si>
     <t>ID</t>
   </si>
@@ -735,6 +735,12 @@
   </si>
   <si>
     <t>4,2,4</t>
+  </si>
+  <si>
+    <t>0.5,0.3,0.2,0.8,0.2,0.1</t>
+  </si>
+  <si>
+    <t>0.2,0.7,0.1,0.8,0.2,0.1</t>
   </si>
 </sst>
 </file>
@@ -1342,6 +1348,9 @@
       <c r="E10">
         <v>0</v>
       </c>
+      <c r="F10" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
@@ -1606,7 +1615,10 @@
         <v>60</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:6">

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0910DFD-BBE2-466F-ABC6-D09555C637AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082EB76E-5EC7-48BC-BE66-8FA2D9CEF6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082EB76E-5EC7-48BC-BE66-8FA2D9CEF6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11BD191-22AA-4BD4-95EB-C3F1F4C3493C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="210">
   <si>
     <t>ID</t>
   </si>
@@ -317,9 +317,6 @@
     <t>#FF2160</t>
   </si>
   <si>
-    <t>AddSinging</t>
-  </si>
-  <si>
     <t>游戏练习</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
   </si>
   <si>
     <t>#4B58FF</t>
-  </si>
-  <si>
-    <t>AddGaming</t>
   </si>
   <si>
     <t>对话练习</t>
@@ -401,9 +395,6 @@
   </si>
   <si>
     <t>第一阶段开始</t>
-  </si>
-  <si>
-    <t>PhaseStart</t>
   </si>
   <si>
     <t>第二阶段开始</t>
@@ -747,12 +738,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -842,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -857,7 +855,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -879,6 +877,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1349,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1605,7 +1607,7 @@
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C26" t="s">
@@ -1618,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1696,13 +1698,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D32" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1713,10 +1715,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1850,7 +1852,7 @@
       <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="14" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1908,7 +1910,7 @@
       <c r="J1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="15" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1932,7 +1934,7 @@
         <v>91</v>
       </c>
       <c r="G2" s="3">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>56</v>
@@ -1940,8 +1942,8 @@
       <c r="I2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>93</v>
+      <c r="K2" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -1949,10 +1951,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>56</v>
@@ -1970,10 +1972,10 @@
         <v>56</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -1981,10 +1983,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>56</v>
@@ -2002,10 +2004,10 @@
         <v>56</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
@@ -2013,13 +2015,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
@@ -2031,13 +2033,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="48" customHeight="1">
@@ -2045,13 +2047,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
@@ -2063,13 +2065,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -2077,13 +2079,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" s="3">
         <v>3</v>
@@ -2095,13 +2097,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
@@ -2109,31 +2111,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
@@ -2141,13 +2143,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -2159,13 +2161,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
@@ -2173,13 +2175,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -2191,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -2205,13 +2207,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -2223,13 +2225,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -2237,13 +2239,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -2255,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
@@ -2269,13 +2271,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
@@ -2287,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
@@ -2301,13 +2303,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -2319,13 +2321,13 @@
         <v>20</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
@@ -2333,13 +2335,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
@@ -2351,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
@@ -2362,13 +2364,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
@@ -2380,13 +2382,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
@@ -2394,31 +2396,31 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
@@ -2426,13 +2428,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -2444,13 +2446,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
@@ -2458,10 +2460,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>56</v>
@@ -2487,10 +2489,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
@@ -2508,7 +2510,7 @@
         <v>56</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
@@ -2516,10 +2518,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>56</v>
@@ -2537,7 +2539,7 @@
         <v>56</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
@@ -2545,13 +2547,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -2563,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
@@ -2577,13 +2579,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -2595,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
@@ -2609,13 +2611,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2627,10 +2629,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
@@ -2638,13 +2640,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -2656,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
@@ -2667,10 +2669,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E26" s="3">
         <v>1</v>
@@ -2682,13 +2684,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2749,28 +2751,28 @@
         <v>87</v>
       </c>
       <c r="K1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P1" t="s">
         <v>157</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>158</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="N1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>161</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2778,13 +2780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2796,10 +2798,10 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2814,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P2" s="3">
         <v>14</v>
@@ -2828,13 +2830,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2846,10 +2848,10 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -2864,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -2878,13 +2880,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2896,10 +2898,10 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -2914,7 +2916,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -2928,13 +2930,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -2946,10 +2948,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2964,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -2979,13 +2981,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -2997,10 +2999,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3014,8 +3016,8 @@
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="O6" t="s">
-        <v>210</v>
+      <c r="O6" s="14" t="s">
+        <v>207</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3030,13 +3032,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3048,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3066,7 +3068,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3081,13 +3083,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3099,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3117,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3132,13 +3134,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3150,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -3168,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3182,13 +3184,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3200,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3218,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3227,7 +3229,7 @@
         <v>7</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -3235,13 +3237,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3253,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3271,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3288,13 +3290,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3306,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3324,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3338,13 +3340,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3356,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3374,7 +3376,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3384,7 +3386,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3417,10 +3419,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3434,7 +3436,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3454,7 +3456,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3474,13 +3476,13 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3505,16 +3507,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3522,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3533,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -3544,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E4">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11BD191-22AA-4BD4-95EB-C3F1F4C3493C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8CDBA-30F2-46A9-8EF4-4295D259CCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="209">
   <si>
     <t>ID</t>
   </si>
@@ -389,9 +389,6 @@
   </si>
   <si>
     <t>昏厥</t>
-  </si>
-  <si>
-    <t>OuttaStamina</t>
   </si>
   <si>
     <t>第一阶段开始</t>
@@ -692,9 +689,6 @@
     <t>VRaisingAddCoopValueEffect</t>
   </si>
   <si>
-    <t>add coop level for goomba</t>
-  </si>
-  <si>
     <t>Upgrade Level for goomba</t>
   </si>
   <si>
@@ -732,6 +726,9 @@
   </si>
   <si>
     <t>0.2,0.7,0.1,0.8,0.2,0.1</t>
+  </si>
+  <si>
+    <t>add coop value for goomba</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1620,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1698,13 +1695,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1715,10 +1712,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -2198,8 +2195,8 @@
       <c r="I10" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>117</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -2207,10 +2204,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>102</v>
@@ -2239,10 +2236,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>102</v>
@@ -2263,7 +2260,7 @@
         <v>112</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
@@ -2271,13 +2268,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
@@ -2292,10 +2289,10 @@
         <v>102</v>
       </c>
       <c r="I13" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
@@ -2303,13 +2300,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -2324,10 +2321,10 @@
         <v>102</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
@@ -2335,10 +2332,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>102</v>
@@ -2356,7 +2353,7 @@
         <v>102</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
@@ -2364,10 +2361,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>102</v>
@@ -2388,7 +2385,7 @@
         <v>112</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
@@ -2396,10 +2393,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>102</v>
@@ -2420,7 +2417,7 @@
         <v>112</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
@@ -2428,10 +2425,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>102</v>
@@ -2452,7 +2449,7 @@
         <v>112</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
@@ -2460,10 +2457,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>56</v>
@@ -2489,10 +2486,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>56</v>
@@ -2518,10 +2515,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>56</v>
@@ -2547,10 +2544,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>102</v>
@@ -2571,7 +2568,7 @@
         <v>112</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
@@ -2579,10 +2576,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>102</v>
@@ -2603,7 +2600,7 @@
         <v>112</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
@@ -2611,28 +2608,28 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
@@ -2640,28 +2637,28 @@
         <v>23</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
@@ -2669,7 +2666,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>102</v>
@@ -2687,10 +2684,10 @@
         <v>102</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2751,28 +2748,28 @@
         <v>87</v>
       </c>
       <c r="K1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1" t="s">
         <v>154</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>155</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>202</v>
+      </c>
+      <c r="O1" t="s">
+        <v>203</v>
+      </c>
+      <c r="P1" t="s">
         <v>156</v>
       </c>
-      <c r="N1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O1" t="s">
-        <v>205</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2780,13 +2777,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" t="s">
         <v>160</v>
-      </c>
-      <c r="C2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" t="s">
-        <v>161</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2798,10 +2795,10 @@
         <v>25</v>
       </c>
       <c r="H2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K2">
         <v>8</v>
@@ -2816,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P2" s="3">
         <v>14</v>
@@ -2830,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2848,10 +2845,10 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K3">
         <v>8</v>
@@ -2866,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P3">
         <v>6</v>
@@ -2880,13 +2877,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2898,10 +2895,10 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K4">
         <v>8</v>
@@ -2916,7 +2913,7 @@
         <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P4">
         <v>6</v>
@@ -2930,13 +2927,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -2948,10 +2945,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2966,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -2981,13 +2978,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" t="s">
         <v>166</v>
       </c>
-      <c r="C6" t="s">
-        <v>167</v>
-      </c>
       <c r="D6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -2999,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -3017,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -3032,13 +3029,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" t="s">
         <v>168</v>
       </c>
-      <c r="C7" t="s">
-        <v>169</v>
-      </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3050,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -3068,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -3083,13 +3080,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" t="s">
         <v>170</v>
       </c>
-      <c r="C8" t="s">
-        <v>171</v>
-      </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3101,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -3119,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -3134,13 +3131,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" t="s">
         <v>172</v>
       </c>
-      <c r="C9" t="s">
-        <v>173</v>
-      </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3152,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -3170,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -3184,13 +3181,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" t="s">
         <v>174</v>
       </c>
-      <c r="C10" t="s">
-        <v>175</v>
-      </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3202,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="K10">
         <v>12</v>
@@ -3220,7 +3217,7 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -3229,7 +3226,7 @@
         <v>7</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -3237,13 +3234,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" t="s">
         <v>177</v>
       </c>
-      <c r="C11" t="s">
-        <v>178</v>
-      </c>
       <c r="D11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3255,10 +3252,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K11">
         <v>12</v>
@@ -3273,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -3290,13 +3287,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" t="s">
         <v>180</v>
       </c>
-      <c r="C12" t="s">
-        <v>181</v>
-      </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3308,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K12">
         <v>12</v>
@@ -3326,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -3340,13 +3337,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" t="s">
         <v>183</v>
       </c>
-      <c r="C13" t="s">
-        <v>184</v>
-      </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3358,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K13">
         <v>12</v>
@@ -3376,7 +3373,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -3419,10 +3416,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" t="s">
         <v>186</v>
-      </c>
-      <c r="F1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3436,7 +3433,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3456,7 +3453,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3476,7 +3473,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -3507,16 +3504,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" t="s">
         <v>191</v>
-      </c>
-      <c r="E1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3524,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3535,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -3546,7 +3543,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E4">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8CDBA-30F2-46A9-8EF4-4295D259CCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3842F3-39F8-45FF-BF77-C58575B1E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="212">
   <si>
     <t>ID</t>
   </si>
@@ -729,6 +729,15 @@
   </si>
   <si>
     <t>add coop value for goomba</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>Graduation_3</t>
+  </si>
+  <si>
+    <t>Graduation_4</t>
   </si>
 </sst>
 </file>
@@ -1939,8 +1948,8 @@
       <c r="I2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="3">
-        <v>0</v>
+      <c r="K2" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -1971,8 +1980,8 @@
       <c r="I3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="K3" s="3">
-        <v>0</v>
+      <c r="K3" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -2195,8 +2204,8 @@
       <c r="I10" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
+      <c r="K10" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -2227,8 +2236,8 @@
       <c r="I11" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="3">
-        <v>0</v>
+      <c r="K11" s="3" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -2355,6 +2364,9 @@
       <c r="I15" s="13" t="s">
         <v>130</v>
       </c>
+      <c r="K15" s="3" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
       <c r="A16" s="3">
@@ -2480,6 +2492,9 @@
       <c r="I19" s="7" t="s">
         <v>92</v>
       </c>
+      <c r="K19" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="3">
@@ -2509,6 +2524,9 @@
       <c r="I20" s="8" t="s">
         <v>95</v>
       </c>
+      <c r="K20" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="3">
@@ -2538,6 +2556,9 @@
       <c r="I21" s="9" t="s">
         <v>98</v>
       </c>
+      <c r="K21" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
       <c r="A22" s="3">
@@ -2631,6 +2652,9 @@
       <c r="I24" s="11" t="s">
         <v>150</v>
       </c>
+      <c r="K24" s="3" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
       <c r="A25" s="3">
@@ -2660,6 +2684,9 @@
       <c r="I25" s="11" t="s">
         <v>152</v>
       </c>
+      <c r="K25" s="3" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="3">
@@ -2691,6 +2718,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3842F3-39F8-45FF-BF77-C58575B1E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AB771C-35F3-4577-8380-DED9458581DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,13 +731,13 @@
     <t>add coop value for goomba</t>
   </si>
   <si>
-    <t>test1</t>
-  </si>
-  <si>
     <t>Graduation_3</t>
   </si>
   <si>
     <t>Graduation_4</t>
+  </si>
+  <si>
+    <t>phase1</t>
   </si>
 </sst>
 </file>
@@ -1949,7 +1949,7 @@
         <v>92</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -1981,7 +1981,7 @@
         <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -2205,7 +2205,7 @@
         <v>112</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -2237,7 +2237,7 @@
         <v>112</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -2653,7 +2653,7 @@
         <v>150</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
@@ -2685,7 +2685,7 @@
         <v>152</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AB771C-35F3-4577-8380-DED9458581DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88454F89-B2BF-4D39-BCFC-E52E7806652E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -3101,7 +3101,10 @@
       <c r="Q7" s="3">
         <v>20</v>
       </c>
-      <c r="R7" s="4"/>
+      <c r="R7" s="4">
+        <f ca="1">R7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88454F89-B2BF-4D39-BCFC-E52E7806652E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F794F3EF-CBF5-4733-A47C-0339ABBDAD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="212">
   <si>
     <t>ID</t>
   </si>
@@ -2720,12 +2720,13 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -2736,15 +2737,16 @@
     <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="15" width="15.85546875" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="14" max="16" width="15.85546875" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2775,32 +2777,35 @@
       <c r="J1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L1" t="s">
         <v>153</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>154</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>155</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>202</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>203</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>156</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>157</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2828,29 +2833,32 @@
       <c r="I2" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L2">
         <v>8</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>100</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>10</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
         <v>204</v>
       </c>
-      <c r="P2" s="3">
+      <c r="Q2" s="3">
         <v>14</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2878,29 +2886,32 @@
       <c r="I3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L3">
         <v>8</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>100</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>10</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>204</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2928,29 +2939,32 @@
       <c r="I4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>100</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>10</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>204</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>6</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2978,30 +2992,33 @@
       <c r="I5" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L5">
         <v>10</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>200</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>25</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
         <v>205</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>6</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>7</v>
       </c>
-      <c r="R5" s="4"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" s="4"/>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3029,30 +3046,33 @@
       <c r="I6" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6">
         <v>10</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5000</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>50</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1</v>
       </c>
-      <c r="O6" s="14" t="s">
+      <c r="P6" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>6</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>20</v>
       </c>
-      <c r="R6" s="4"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" s="4"/>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3080,33 +3100,36 @@
       <c r="I7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7">
         <v>10</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>5000</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>50</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>2</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>205</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>6</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>20</v>
       </c>
-      <c r="R7" s="4">
-        <f ca="1">R7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7" s="4">
+        <f ca="1">S7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3134,30 +3157,33 @@
       <c r="I8" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L8">
         <v>10</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>5000</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>50</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
         <v>205</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>6</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20</v>
       </c>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8" s="4"/>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3185,29 +3211,32 @@
       <c r="I9" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L9">
         <v>10</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>5000</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>50</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>205</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>6</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3235,32 +3264,35 @@
       <c r="I10" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>9000</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>80</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>2</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>205</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>6</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>7</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="S10" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3288,32 +3320,35 @@
       <c r="I11" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11">
         <v>12</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>9000</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>80</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
         <v>205</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>6</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>7</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3341,29 +3376,32 @@
       <c r="I12" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L12">
         <v>12</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>9000</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>80</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>205</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>6</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3391,25 +3429,28 @@
       <c r="I13" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L13">
         <v>12</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>9000</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>80</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>2</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>205</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>6</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>7</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F794F3EF-CBF5-4733-A47C-0339ABBDAD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348B95D4-E861-4A4E-AC1B-3593F5BB392D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="246">
   <si>
     <t>ID</t>
   </si>
@@ -578,18 +578,12 @@
     <t>FailEvent</t>
   </si>
   <si>
-    <t>Conditions</t>
-  </si>
-  <si>
     <t>歌回</t>
   </si>
   <si>
     <t>Stream</t>
   </si>
   <si>
-    <t>#AB0580</t>
-  </si>
-  <si>
     <t>游戏回</t>
   </si>
   <si>
@@ -605,9 +599,6 @@
     <t>第一阶段歌力</t>
   </si>
   <si>
-    <t>水友联动回</t>
-  </si>
-  <si>
     <t>第一阶段游戏力</t>
   </si>
   <si>
@@ -620,45 +611,21 @@
     <t>健身环挑战回</t>
   </si>
   <si>
-    <t>第一阶段体力</t>
-  </si>
-  <si>
-    <t>耐久歌回</t>
-  </si>
-  <si>
     <t>第二阶段歌力</t>
   </si>
   <si>
-    <t>0, 2</t>
-  </si>
-  <si>
     <t>段位挑战回</t>
   </si>
   <si>
     <t>第二阶段游戏</t>
   </si>
   <si>
-    <t>#AB0581</t>
-  </si>
-  <si>
-    <t>故事会</t>
-  </si>
-  <si>
     <t>第二阶段杂谈</t>
   </si>
   <si>
-    <t>#AB0582</t>
-  </si>
-  <si>
-    <t>冲舰回</t>
-  </si>
-  <si>
     <t>第二阶段营收</t>
   </si>
   <si>
-    <t>#AB0583</t>
-  </si>
-  <si>
     <t>NameOrID</t>
   </si>
   <si>
@@ -738,6 +705,141 @@
   </si>
   <si>
     <t>phase1</t>
+  </si>
+  <si>
+    <t>ExtraTarget</t>
+  </si>
+  <si>
+    <t>AttributeBonus</t>
+  </si>
+  <si>
+    <t>2,4,2</t>
+  </si>
+  <si>
+    <t>2,2,4</t>
+  </si>
+  <si>
+    <t>5,2,3</t>
+  </si>
+  <si>
+    <t>水友联动游戏回</t>
+  </si>
+  <si>
+    <t>2,5,3</t>
+  </si>
+  <si>
+    <t>2,2,6</t>
+  </si>
+  <si>
+    <t>水友歌回</t>
+  </si>
+  <si>
+    <t>6,3,3</t>
+  </si>
+  <si>
+    <t>水友游戏回</t>
+  </si>
+  <si>
+    <t>3,6,3</t>
+  </si>
+  <si>
+    <t>视频鉴赏回</t>
+  </si>
+  <si>
+    <t>3,3,6</t>
+  </si>
+  <si>
+    <t>代抽回</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>水友投稿回</t>
+  </si>
+  <si>
+    <t>第三阶段粉丝</t>
+  </si>
+  <si>
+    <t>生日回</t>
+  </si>
+  <si>
+    <t>第三阶段舰长</t>
+  </si>
+  <si>
+    <t>5,3,4</t>
+  </si>
+  <si>
+    <t>粉丝礼物回</t>
+  </si>
+  <si>
+    <t>第三阶段营收</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>第三阶段体力</t>
+  </si>
+  <si>
+    <t>3,5,4</t>
+  </si>
+  <si>
+    <t>光暗歌会</t>
+  </si>
+  <si>
+    <t>歌力加成结局</t>
+  </si>
+  <si>
+    <t>7,4,4</t>
+  </si>
+  <si>
+    <t>游戏力加成结局</t>
+  </si>
+  <si>
+    <t>4,7,4</t>
+  </si>
+  <si>
+    <t>清楚聊天室</t>
+  </si>
+  <si>
+    <t>杂谈力加成结局</t>
+  </si>
+  <si>
+    <t>4,4,7</t>
+  </si>
+  <si>
+    <t>人头麦回</t>
+  </si>
+  <si>
+    <t>营收加成结局</t>
+  </si>
+  <si>
+    <t>6,4,5</t>
+  </si>
+  <si>
+    <t>健身环耐久回</t>
+  </si>
+  <si>
+    <t>体力加成结局</t>
+  </si>
+  <si>
+    <t>4,6,5</t>
+  </si>
+  <si>
+    <t>百舰回</t>
+  </si>
+  <si>
+    <t>舰长加成结局</t>
+  </si>
+  <si>
+    <t>新衣回嘉宾</t>
+  </si>
+  <si>
+    <t>好感度加成结局</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1626,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1704,13 +1806,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1721,10 +1823,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1949,7 +2051,7 @@
         <v>92</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -1981,7 +2083,7 @@
         <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -2205,7 +2307,7 @@
         <v>112</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -2237,7 +2339,7 @@
         <v>112</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -2653,7 +2755,7 @@
         <v>150</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
@@ -2685,7 +2787,7 @@
         <v>152</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
@@ -2693,7 +2795,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>102</v>
@@ -2711,10 +2813,10 @@
         <v>102</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2726,7 +2828,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -2746,7 +2848,7 @@
     <col min="19" max="19" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2787,36 +2889,39 @@
         <v>154</v>
       </c>
       <c r="N1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O1" t="s">
         <v>155</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>192</v>
+      </c>
+      <c r="R1" t="s">
+        <v>156</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="T1" t="s">
         <v>202</v>
       </c>
-      <c r="P1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>156</v>
-      </c>
-      <c r="R1" t="s">
-        <v>157</v>
-      </c>
-      <c r="S1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" t="s">
         <v>159</v>
-      </c>
-      <c r="C2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" t="s">
-        <v>160</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2825,16 +2930,16 @@
         <v>91</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2843,33 +2948,39 @@
         <v>100</v>
       </c>
       <c r="N2">
+        <v>200</v>
+      </c>
+      <c r="O2">
         <v>10</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q2" s="3">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="R2">
         <v>14</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2878,16 +2989,16 @@
         <v>91</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2896,33 +3007,39 @@
         <v>100</v>
       </c>
       <c r="N3">
+        <v>200</v>
+      </c>
+      <c r="O3">
         <v>10</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q3">
+      <c r="Q3" t="s">
+        <v>203</v>
+      </c>
+      <c r="R3">
         <v>6</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -2931,16 +3048,16 @@
         <v>91</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2949,33 +3066,39 @@
         <v>100</v>
       </c>
       <c r="N4">
+        <v>200</v>
+      </c>
+      <c r="O4">
         <v>10</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>204</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>6</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -2984,16 +3107,16 @@
         <v>91</v>
       </c>
       <c r="G5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -3002,34 +3125,39 @@
         <v>200</v>
       </c>
       <c r="N5">
+        <v>300</v>
+      </c>
+      <c r="O5">
         <v>25</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q5">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>194</v>
+      </c>
+      <c r="R5" s="3">
         <v>6</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="4">
         <v>7</v>
       </c>
-      <c r="S5" s="4"/>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3041,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -3056,34 +3184,39 @@
         <v>5000</v>
       </c>
       <c r="N6">
+        <v>6000</v>
+      </c>
+      <c r="O6">
         <v>50</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6" s="14" t="s">
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
         <v>205</v>
       </c>
-      <c r="Q6">
+      <c r="R6" s="3">
         <v>6</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="4">
         <v>20</v>
       </c>
-      <c r="S6" s="4"/>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -3095,13 +3228,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -3110,37 +3243,39 @@
         <v>5000</v>
       </c>
       <c r="N7">
+        <v>6000</v>
+      </c>
+      <c r="O7">
         <v>50</v>
       </c>
-      <c r="O7">
-        <v>2</v>
-      </c>
-      <c r="P7" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q7">
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>207</v>
+      </c>
+      <c r="R7" s="3">
         <v>6</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="4">
         <v>20</v>
       </c>
-      <c r="S7" s="4">
-        <f ca="1">S7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -3152,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>161</v>
+        <v>98</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -3167,34 +3302,39 @@
         <v>5000</v>
       </c>
       <c r="N8">
+        <v>6000</v>
+      </c>
+      <c r="O8">
         <v>50</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q8">
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>208</v>
+      </c>
+      <c r="R8" s="3">
         <v>6</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="4">
         <v>20</v>
       </c>
-      <c r="S8" s="4"/>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -3206,48 +3346,54 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M9">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="N9">
-        <v>50</v>
+        <v>22000</v>
       </c>
       <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q9">
+        <v>80</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>210</v>
+      </c>
+      <c r="R9">
         <v>6</v>
       </c>
-      <c r="R9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="S9">
+        <v>7</v>
+      </c>
+      <c r="T9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3259,51 +3405,54 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L10">
         <v>12</v>
       </c>
       <c r="M10">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="N10">
+        <v>22000</v>
+      </c>
+      <c r="O10">
         <v>80</v>
       </c>
-      <c r="O10">
-        <v>2</v>
-      </c>
-      <c r="P10" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q10">
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>212</v>
+      </c>
+      <c r="R10">
         <v>6</v>
       </c>
-      <c r="R10">
+      <c r="S10" s="4">
         <v>7</v>
       </c>
-      <c r="S10" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -3315,51 +3464,54 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L11">
         <v>12</v>
       </c>
       <c r="M11">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="N11">
+        <v>22000</v>
+      </c>
+      <c r="O11">
         <v>80</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q11">
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>214</v>
+      </c>
+      <c r="R11">
         <v>6</v>
       </c>
-      <c r="R11">
+      <c r="S11" s="4">
         <v>7</v>
       </c>
-      <c r="S11" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3371,48 +3523,54 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L12">
         <v>12</v>
       </c>
       <c r="M12">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="N12">
+        <v>22000</v>
+      </c>
+      <c r="O12">
         <v>80</v>
       </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q12">
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>216</v>
+      </c>
+      <c r="R12">
         <v>6</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3424,34 +3582,630 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="L13">
         <v>12</v>
       </c>
       <c r="M13">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="N13">
-        <v>80</v>
+        <v>30000</v>
       </c>
       <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13">
         <v>2</v>
       </c>
-      <c r="P13" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q13">
+      <c r="Q13" t="s">
+        <v>214</v>
+      </c>
+      <c r="R13">
         <v>6</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>7</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" t="s">
+        <v>92</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+      <c r="M14">
+        <v>20000</v>
+      </c>
+      <c r="N14">
+        <v>30000</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>221</v>
+      </c>
+      <c r="R14">
+        <v>6</v>
+      </c>
+      <c r="S14">
+        <v>7</v>
+      </c>
+      <c r="T14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15">
+        <v>20000</v>
+      </c>
+      <c r="N15">
+        <v>30000</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>224</v>
+      </c>
+      <c r="R15">
+        <v>6</v>
+      </c>
+      <c r="S15">
+        <v>7</v>
+      </c>
+      <c r="T15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L16">
+        <v>12</v>
+      </c>
+      <c r="M16">
+        <v>20000</v>
+      </c>
+      <c r="N16">
+        <v>30000</v>
+      </c>
+      <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>226</v>
+      </c>
+      <c r="R16">
+        <v>6</v>
+      </c>
+      <c r="S16">
+        <v>7</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" t="s">
+        <v>92</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L17">
+        <v>15</v>
+      </c>
+      <c r="M17">
+        <v>40000</v>
+      </c>
+      <c r="N17">
+        <v>50000</v>
+      </c>
+      <c r="O17">
+        <v>130</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>229</v>
+      </c>
+      <c r="R17">
+        <v>6</v>
+      </c>
+      <c r="S17">
+        <v>7</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L18">
+        <v>15</v>
+      </c>
+      <c r="M18">
+        <v>40000</v>
+      </c>
+      <c r="N18">
+        <v>50000</v>
+      </c>
+      <c r="O18">
+        <v>130</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>231</v>
+      </c>
+      <c r="R18">
+        <v>6</v>
+      </c>
+      <c r="S18">
+        <v>7</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>159</v>
+      </c>
+      <c r="I19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L19">
+        <v>15</v>
+      </c>
+      <c r="M19">
+        <v>40000</v>
+      </c>
+      <c r="N19">
+        <v>50000</v>
+      </c>
+      <c r="O19">
+        <v>130</v>
+      </c>
+      <c r="P19">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>234</v>
+      </c>
+      <c r="R19">
+        <v>6</v>
+      </c>
+      <c r="S19">
+        <v>7</v>
+      </c>
+      <c r="T19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>159</v>
+      </c>
+      <c r="I20" t="s">
+        <v>92</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20">
+        <v>15</v>
+      </c>
+      <c r="M20">
+        <v>40000</v>
+      </c>
+      <c r="N20">
+        <v>50000</v>
+      </c>
+      <c r="O20">
+        <v>130</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>237</v>
+      </c>
+      <c r="R20">
+        <v>6</v>
+      </c>
+      <c r="S20">
+        <v>7</v>
+      </c>
+      <c r="T20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" t="s">
+        <v>95</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L21">
+        <v>15</v>
+      </c>
+      <c r="M21">
+        <v>40000</v>
+      </c>
+      <c r="N21">
+        <v>50000</v>
+      </c>
+      <c r="O21">
+        <v>130</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>240</v>
+      </c>
+      <c r="R21">
+        <v>6</v>
+      </c>
+      <c r="S21">
+        <v>7</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L22">
+        <v>15</v>
+      </c>
+      <c r="M22">
+        <v>40000</v>
+      </c>
+      <c r="N22">
+        <v>50000</v>
+      </c>
+      <c r="O22">
+        <v>130</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>237</v>
+      </c>
+      <c r="R22">
+        <v>6</v>
+      </c>
+      <c r="S22">
+        <v>7</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L23">
+        <v>15</v>
+      </c>
+      <c r="M23">
+        <v>40000</v>
+      </c>
+      <c r="N23">
+        <v>50000</v>
+      </c>
+      <c r="O23">
+        <v>130</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>245</v>
+      </c>
+      <c r="R23">
+        <v>6</v>
+      </c>
+      <c r="S23">
+        <v>7</v>
+      </c>
+      <c r="T23">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3488,10 +4242,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3505,7 +4259,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3525,7 +4279,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3545,7 +4299,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -3576,16 +4330,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3593,10 +4347,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3604,7 +4358,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -3615,7 +4369,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E4">
         <v>4</v>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB17F89-48D2-45B9-9944-2DC22ED8AEC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70553E5D-D106-4EE7-9BC2-538369BC8EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="464">
   <si>
     <t>ID</t>
   </si>
@@ -118,39 +118,39 @@
     <t>歌力提升率+X%</t>
   </si>
   <si>
+    <t>CASingingAbilityGainEfficiency</t>
+  </si>
+  <si>
+    <t>游戏力提升率+X%</t>
+  </si>
+  <si>
+    <t>CAGamingAbilityGainEfficiency</t>
+  </si>
+  <si>
+    <t>杂谈力提升率+X%</t>
+  </si>
+  <si>
+    <t>CAChattingAbilityGainEfficiency</t>
+  </si>
+  <si>
+    <t>歌力提升转化率+X%</t>
+  </si>
+  <si>
     <t>CASingingAbilityConversionRatio</t>
   </si>
   <si>
-    <t>游戏力提升率+X%</t>
+    <t>游戏力转化率+X%</t>
   </si>
   <si>
     <t>CAGamingAbilityConversionRatio</t>
   </si>
   <si>
-    <t>杂谈力提升率+X%</t>
+    <t>杂谈力转化率+X%</t>
   </si>
   <si>
     <t>CAChattingAbilityConversionRatio</t>
   </si>
   <si>
-    <t>歌力提升转化率+X%</t>
-  </si>
-  <si>
-    <t>CASingingAbilityGainEfficiency</t>
-  </si>
-  <si>
-    <t>游戏力转化率+X%</t>
-  </si>
-  <si>
-    <t>CAGamingAbilityGainEfficiency</t>
-  </si>
-  <si>
-    <t>杂谈力转化率+X%</t>
-  </si>
-  <si>
-    <t>CAChattingAbilityGainEfficiency</t>
-  </si>
-  <si>
     <t>粉丝数+X</t>
   </si>
   <si>
@@ -184,15 +184,12 @@
     <t>VRaisingPickPhaseEndingEffect</t>
   </si>
   <si>
-    <t>加遗物0</t>
+    <t>获得遗物</t>
   </si>
   <si>
     <t>VRaisingAddRelicEffect</t>
   </si>
   <si>
-    <t>加遗物1</t>
-  </si>
-  <si>
     <t>追加事件Test</t>
   </si>
   <si>
@@ -217,7 +214,7 @@
     <t>VRaisingAddSelectedFrom3Effect</t>
   </si>
   <si>
-    <t>0.5,0.3,0.1,0.1,0.05,0.01</t>
+    <t>0.6,0.3,0.1,0.1,0.05,0.01</t>
   </si>
   <si>
     <t>进入结局</t>
@@ -262,22 +259,133 @@
     <t>VRaisingDeleteCardEffect</t>
   </si>
   <si>
-    <t>随机获得一张A类型卡</t>
-  </si>
-  <si>
-    <t>VRaisingAddRandomCardEffect</t>
-  </si>
-  <si>
-    <t>0.5,0.3,0.1,0,0,0</t>
-  </si>
-  <si>
-    <t>随机获得一张M类型卡</t>
-  </si>
-  <si>
-    <t>随机获得一张红温相关卡</t>
-  </si>
-  <si>
-    <t>随机获得一张幽默相关卡</t>
+    <t>获得一张A类型卡</t>
+  </si>
+  <si>
+    <t>0.6,0.3,0.1,0,0,0</t>
+  </si>
+  <si>
+    <t>获得一张M类型卡</t>
+  </si>
+  <si>
+    <t>获得一张红温相关卡</t>
+  </si>
+  <si>
+    <t>获得一张幽默相关卡</t>
+  </si>
+  <si>
+    <t>随机强化一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeRandomCardEffect</t>
+  </si>
+  <si>
+    <t>选择一张营收牌获得</t>
+  </si>
+  <si>
+    <t>最大体力值+X</t>
+  </si>
+  <si>
+    <t>VRaisingAddAttributeMaxValueEffect</t>
+  </si>
+  <si>
+    <t>随机获得一个消耗品</t>
+  </si>
+  <si>
+    <t>VRaisingAddRandomConsumableEffect</t>
+  </si>
+  <si>
+    <t>0.6,0.3,0.1</t>
+  </si>
+  <si>
+    <t>选择一个消耗品获得</t>
+  </si>
+  <si>
+    <t>VRaisingAddSelectFrom3ConsumableEffect</t>
+  </si>
+  <si>
+    <t>获得一张高稀有卡牌获得</t>
+  </si>
+  <si>
+    <t>0,0,1,0,0,0</t>
+  </si>
+  <si>
+    <t>小室好感升级</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeCoopLevel</t>
+  </si>
+  <si>
+    <t>雪王好感升级</t>
+  </si>
+  <si>
+    <t>mama好感升级</t>
+  </si>
+  <si>
+    <t>井井好感升级</t>
+  </si>
+  <si>
+    <t>柚子茶好感升级</t>
+  </si>
+  <si>
+    <t>获得卡牌</t>
+  </si>
+  <si>
+    <t>VAddSpecifiedCardEffect</t>
+  </si>
+  <si>
+    <t>协助者好感升级</t>
+  </si>
+  <si>
+    <t>选择一张强化过的卡牌获得</t>
+  </si>
+  <si>
+    <t>0.4,0.5,0.1,1,1,1</t>
+  </si>
+  <si>
+    <t>进入商店</t>
+  </si>
+  <si>
+    <t>VRaisingEnterStoreEffect</t>
+  </si>
+  <si>
+    <t>获得舰长数X%的歌力</t>
+  </si>
+  <si>
+    <t>VRaisingAddPercentageFromAttributeEffect</t>
+  </si>
+  <si>
+    <t>CASingingAbility,CAMembershipCount</t>
+  </si>
+  <si>
+    <t>获得舰长数X%的游戏力</t>
+  </si>
+  <si>
+    <t>CAGamingAbility,CAMembershipCount</t>
+  </si>
+  <si>
+    <t>获得舰长数X%的杂谈力</t>
+  </si>
+  <si>
+    <t>CAChattingAbility,CAMembershipCount</t>
+  </si>
+  <si>
+    <t>获得粉丝数X%的歌力</t>
+  </si>
+  <si>
+    <t>CASingingAbility,CAFollowerCount</t>
+  </si>
+  <si>
+    <t>获得粉丝数X%的游戏力</t>
+  </si>
+  <si>
+    <t>CAGamingAbility,CAFollowerCount</t>
+  </si>
+  <si>
+    <t>获得粉丝数X%的杂谈力</t>
+  </si>
+  <si>
+    <t>CAChattingAbility,CAFollowerCount</t>
   </si>
   <si>
     <t>Duration</t>
@@ -346,6 +454,9 @@
     <t>Stamina</t>
   </si>
   <si>
+    <t>singlive</t>
+  </si>
+  <si>
     <t>#FF2160</t>
   </si>
   <si>
@@ -358,6 +469,9 @@
     <t>游戏回</t>
   </si>
   <si>
+    <t>gamelive</t>
+  </si>
+  <si>
     <t>#4B58FF</t>
   </si>
   <si>
@@ -367,6 +481,9 @@
     <t>杂谈回</t>
   </si>
   <si>
+    <t>chatlive</t>
+  </si>
+  <si>
     <t>#FFB200</t>
   </si>
   <si>
@@ -388,7 +505,10 @@
     <t>5,2,3</t>
   </si>
   <si>
-    <t>水友联动游戏回</t>
+    <t>Stream,0,2</t>
+  </si>
+  <si>
+    <t>游戏耐久回</t>
   </si>
   <si>
     <t>第一阶段游戏力</t>
@@ -397,7 +517,7 @@
     <t>2,5,3</t>
   </si>
   <si>
-    <t>Work,4</t>
+    <t>Stream,1,2</t>
   </si>
   <si>
     <t>棉花糖回</t>
@@ -409,6 +529,9 @@
     <t>2,2,6</t>
   </si>
   <si>
+    <t>Stream,2,2</t>
+  </si>
+  <si>
     <t>水友歌回</t>
   </si>
   <si>
@@ -418,78 +541,93 @@
     <t>6,3,3</t>
   </si>
   <si>
+    <t>水友游戏回</t>
+  </si>
+  <si>
+    <t>第二阶段游戏</t>
+  </si>
+  <si>
+    <t>3,6,3</t>
+  </si>
+  <si>
+    <t>视频鉴赏回</t>
+  </si>
+  <si>
+    <t>第二阶段杂谈</t>
+  </si>
+  <si>
+    <t>3,3,6</t>
+  </si>
+  <si>
+    <t>代抽回</t>
+  </si>
+  <si>
+    <t>第二阶段营收</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>Work,2</t>
+  </si>
+  <si>
+    <t>水友投稿回</t>
+  </si>
+  <si>
+    <t>第三阶段粉丝</t>
+  </si>
+  <si>
+    <t>Work,3</t>
+  </si>
+  <si>
+    <t>生日回</t>
+  </si>
+  <si>
+    <t>第三阶段舰长</t>
+  </si>
+  <si>
+    <t>5,3,4</t>
+  </si>
+  <si>
+    <t>Stream,-1,3</t>
+  </si>
+  <si>
+    <t>粉丝礼物回</t>
+  </si>
+  <si>
+    <t>第三阶段营收</t>
+  </si>
+  <si>
+    <t>4,4,4</t>
+  </si>
+  <si>
+    <t>健身环挑战回</t>
+  </si>
+  <si>
+    <t>第三阶段体力</t>
+  </si>
+  <si>
+    <t>3,5,4</t>
+  </si>
+  <si>
+    <t>Rest,4</t>
+  </si>
+  <si>
+    <t>Practice,3</t>
+  </si>
+  <si>
+    <t>水火歌会</t>
+  </si>
+  <si>
+    <t>歌力加成结局</t>
+  </si>
+  <si>
+    <t>7,4,4</t>
+  </si>
+  <si>
     <t>Stream,0,3</t>
   </si>
   <si>
-    <t>水友游戏回</t>
-  </si>
-  <si>
-    <t>第二阶段游戏</t>
-  </si>
-  <si>
-    <t>3,6,3</t>
-  </si>
-  <si>
-    <t>视频鉴赏回</t>
-  </si>
-  <si>
-    <t>第二阶段杂谈</t>
-  </si>
-  <si>
-    <t>3,3,6</t>
-  </si>
-  <si>
-    <t>代抽回</t>
-  </si>
-  <si>
-    <t>第二阶段营收</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>水友投稿回</t>
-  </si>
-  <si>
-    <t>第三阶段粉丝</t>
-  </si>
-  <si>
-    <t>生日回</t>
-  </si>
-  <si>
-    <t>第三阶段舰长</t>
-  </si>
-  <si>
-    <t>5,3,4</t>
-  </si>
-  <si>
-    <t>粉丝礼物回</t>
-  </si>
-  <si>
-    <t>第三阶段营收</t>
-  </si>
-  <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>健身环挑战回</t>
-  </si>
-  <si>
-    <t>第三阶段体力</t>
-  </si>
-  <si>
-    <t>3,5,4</t>
-  </si>
-  <si>
-    <t>光暗歌会</t>
-  </si>
-  <si>
-    <t>歌力加成结局</t>
-  </si>
-  <si>
-    <t>7,4,4</t>
-  </si>
-  <si>
     <t>段位挑战回</t>
   </si>
   <si>
@@ -499,6 +637,9 @@
     <t>4,7,4</t>
   </si>
   <si>
+    <t>Stream,1,3</t>
+  </si>
+  <si>
     <t>清楚聊天室</t>
   </si>
   <si>
@@ -508,6 +649,9 @@
     <t>4,4,7</t>
   </si>
   <si>
+    <t>Stream,2,3</t>
+  </si>
+  <si>
     <t>人头麦回</t>
   </si>
   <si>
@@ -517,15 +661,21 @@
     <t>6,4,5</t>
   </si>
   <si>
+    <t>Outside,1</t>
+  </si>
+  <si>
     <t>健身环耐久回</t>
   </si>
   <si>
-    <t>体力加成结局</t>
+    <t>粉丝加成结局</t>
   </si>
   <si>
     <t>4,6,5</t>
   </si>
   <si>
+    <t>Rest,2</t>
+  </si>
+  <si>
     <t>百舰回</t>
   </si>
   <si>
@@ -544,7 +694,10 @@
     <t>声乐练习</t>
   </si>
   <si>
-    <t>歌力+20</t>
+    <t>歌力+18</t>
+  </si>
+  <si>
+    <t>singpractice</t>
   </si>
   <si>
     <t>SingPractice</t>
@@ -553,7 +706,10 @@
     <t>游戏练习</t>
   </si>
   <si>
-    <t>游戏力+20</t>
+    <t>游戏力+18</t>
+  </si>
+  <si>
+    <t>gamepractice</t>
   </si>
   <si>
     <t>GamePractice</t>
@@ -562,7 +718,10 @@
     <t>对话练习</t>
   </si>
   <si>
-    <t>杂谈力+20</t>
+    <t>杂谈力+18</t>
+  </si>
+  <si>
+    <t>chatpractice</t>
   </si>
   <si>
     <t>ChatPractice</t>
@@ -577,6 +736,9 @@
     <t>Rest</t>
   </si>
   <si>
+    <t>rest</t>
+  </si>
+  <si>
     <t>#00B050</t>
   </si>
   <si>
@@ -646,15 +808,13 @@
     <t>兼职</t>
   </si>
   <si>
-    <t>沪币+50，粉丝+100
-沪币+90
-金钱+50，获得一张卡</t>
+    <t>获得沪币，并且触发其他效果</t>
   </si>
   <si>
     <t>Work</t>
   </si>
   <si>
-    <t>#E5FD1F</t>
+    <t>#A122FB</t>
   </si>
   <si>
     <t>Work1</t>
@@ -663,92 +823,30 @@
     <t>剪辑切片</t>
   </si>
   <si>
-    <t>粉丝+100，金钱+15，从卡组中删除一张牌</t>
+    <t>获得沪币，并且选择卡牌获得</t>
   </si>
   <si>
     <t>Work2</t>
   </si>
   <si>
-    <t>购物</t>
-  </si>
-  <si>
-    <t>进入商店界面</t>
+    <t>外出购物</t>
   </si>
   <si>
     <t>Outside</t>
   </si>
   <si>
+    <t>store</t>
+  </si>
+  <si>
     <t>#0BF30B</t>
   </si>
   <si>
+    <t>Store</t>
+  </si>
+  <si>
     <t>歌回成功事件</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>粉丝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，金钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，舰长</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，获得一张卡</t>
-    </r>
-  </si>
-  <si>
     <t>SingSuccess</t>
   </si>
   <si>
@@ -764,28 +862,37 @@
     <t>进阶唱歌练习</t>
   </si>
   <si>
-    <t>歌力+30，获得一张卡</t>
+    <t>歌力+25</t>
+  </si>
+  <si>
+    <t>SingPractice2</t>
   </si>
   <si>
     <t>进阶游戏练习</t>
   </si>
   <si>
-    <t>游戏力+30，获得一张卡</t>
+    <t>游戏力+25</t>
+  </si>
+  <si>
+    <t>GamePractice2</t>
   </si>
   <si>
     <t>进阶杂谈练习</t>
   </si>
   <si>
-    <t>杂谈力+30，获得一张卡</t>
+    <t>杂谈力+25</t>
+  </si>
+  <si>
+    <t>ChatPractice2</t>
   </si>
   <si>
     <t>毕业1</t>
   </si>
   <si>
-    <t>第一阶段失败</t>
-  </si>
-  <si>
-    <t>Graduation_1</t>
+    <t>毕业结局</t>
+  </si>
+  <si>
+    <t>Graduation</t>
   </si>
   <si>
     <t>毕业2</t>
@@ -803,43 +910,67 @@
     <t>#D1CECE</t>
   </si>
   <si>
+    <t>phase3</t>
+  </si>
+  <si>
     <t>结局阶段开始</t>
   </si>
   <si>
     <t>#D2CECE</t>
   </si>
   <si>
-    <t>雪王好感度增加事件</t>
+    <t>phase4</t>
+  </si>
+  <si>
+    <t>找血王喝酒</t>
+  </si>
+  <si>
+    <t>至尊血王好感度+5</t>
   </si>
   <si>
     <t>Coop</t>
   </si>
   <si>
+    <t>coop</t>
+  </si>
+  <si>
     <t>#F567ED</t>
   </si>
   <si>
     <t>XuewangMeet1</t>
   </si>
   <si>
-    <t>小室好感度增加事件</t>
+    <t>找小室玩</t>
+  </si>
+  <si>
+    <t>小室好感度+5</t>
   </si>
   <si>
     <t>XiaoShiMeet1</t>
   </si>
   <si>
-    <t>井井好感度增加事件</t>
+    <t>和井井练歌</t>
+  </si>
+  <si>
+    <t>井井好感度+5</t>
   </si>
   <si>
     <t>##Meet1</t>
   </si>
   <si>
-    <t>奶茶好感度增加事件</t>
+    <t>和柚茶打游戏</t>
+  </si>
+  <si>
+    <t>柚子茶好感度+5</t>
   </si>
   <si>
     <t>YuzuMeet1</t>
   </si>
   <si>
-    <t>画师好感度增加事件</t>
+    <t>和糯糯聊天</t>
+  </si>
+  <si>
+    <t>画师mama好感度+5</t>
   </si>
   <si>
     <t>MamaMeet1</t>
@@ -848,9 +979,369 @@
     <t>大白猫好感度增加事件</t>
   </si>
   <si>
+    <t>大白猫好感度+5</t>
+  </si>
+  <si>
     <t>外出吃饭</t>
   </si>
   <si>
+    <t>消耗沪币回复体力，并且触发其他效果</t>
+  </si>
+  <si>
+    <t>Money</t>
+  </si>
+  <si>
+    <t>lamian</t>
+  </si>
+  <si>
+    <t>Lamian</t>
+  </si>
+  <si>
+    <t>动态营业</t>
+  </si>
+  <si>
+    <t>获得粉丝，并且触发其他效果</t>
+  </si>
+  <si>
+    <t>Work3</t>
+  </si>
+  <si>
+    <t>和小室约会1</t>
+  </si>
+  <si>
+    <t>最大体力值+5，粉丝+300</t>
+  </si>
+  <si>
+    <t>deeplove</t>
+  </si>
+  <si>
+    <t>XiaoShiLove_1</t>
+  </si>
+  <si>
+    <t>和小室约会2</t>
+  </si>
+  <si>
+    <t>获得遗物小室的头绳，回复10点体力</t>
+  </si>
+  <si>
+    <t>XiaoShiLove_2</t>
+  </si>
+  <si>
+    <t>和小室约会3</t>
+  </si>
+  <si>
+    <t>最大体力值+5，选择一张高稀有度卡获得</t>
+  </si>
+  <si>
+    <t>XiaoShiLove_3</t>
+  </si>
+  <si>
+    <t>和小室约会4</t>
+  </si>
+  <si>
+    <t>获得遗物小室的玫瑰，回复15点体力</t>
+  </si>
+  <si>
+    <t>XiaoShiLove_4</t>
+  </si>
+  <si>
+    <t>和血王约会1</t>
+  </si>
+  <si>
+    <t>杂谈力提升率+3%，获得卡牌“好娇娇”</t>
+  </si>
+  <si>
+    <t>XuewangLove_1</t>
+  </si>
+  <si>
+    <t>和血王约会2</t>
+  </si>
+  <si>
+    <t>获得遗物雪王的狗，随机强化一张卡</t>
+  </si>
+  <si>
+    <t>XuewangLove_2</t>
+  </si>
+  <si>
+    <t>和血王约会3</t>
+  </si>
+  <si>
+    <t>杂谈力提升率+3%，获得卡牌“窝里横”</t>
+  </si>
+  <si>
+    <t>XuewangLove_3</t>
+  </si>
+  <si>
+    <t>和血王约会4</t>
+  </si>
+  <si>
+    <t>获得遗物雪王的心脏，压力-1</t>
+  </si>
+  <si>
+    <t>XuewangLove_4</t>
+  </si>
+  <si>
+    <t>和井井约会1</t>
+  </si>
+  <si>
+    <t>歌力提升率+3%，获得卡牌“养”</t>
+  </si>
+  <si>
+    <t>##Love_1</t>
+  </si>
+  <si>
+    <t>和井井约会2</t>
+  </si>
+  <si>
+    <t>获得遗物井井的麦克风，粉丝+200</t>
+  </si>
+  <si>
+    <t>##Love_2</t>
+  </si>
+  <si>
+    <t>和井井约会3</t>
+  </si>
+  <si>
+    <t>歌力提升率+3%，获得卡牌“gachi距离”</t>
+  </si>
+  <si>
+    <t>##Love_3</t>
+  </si>
+  <si>
+    <t>和井井约会4</t>
+  </si>
+  <si>
+    <t>获得遗物井井的光环，粉丝+300</t>
+  </si>
+  <si>
+    <t>##Love_4</t>
+  </si>
+  <si>
+    <t>和糯糯约会1</t>
+  </si>
+  <si>
+    <t>舰长+5，粉丝+200，获得卡牌“工作音”</t>
+  </si>
+  <si>
+    <t>MamaLove_1</t>
+  </si>
+  <si>
+    <t>和糯糯约会2</t>
+  </si>
+  <si>
+    <t>获得遗物糯糯的画笔，沪币+50</t>
+  </si>
+  <si>
+    <t>MamaLove_2</t>
+  </si>
+  <si>
+    <t>和糯糯约会3</t>
+  </si>
+  <si>
+    <t>舰长+10，粉丝+300，获得卡牌“摸鱼”</t>
+  </si>
+  <si>
+    <t>MamaLove_3</t>
+  </si>
+  <si>
+    <t>和糯糯约会4</t>
+  </si>
+  <si>
+    <t>获得遗物糯糯的画板，沪币+200</t>
+  </si>
+  <si>
+    <t>MamaLove_4</t>
+  </si>
+  <si>
+    <t>和柚茶约会1</t>
+  </si>
+  <si>
+    <t>游戏力提升率+3%获得卡牌“战略规划”
+限定晚上</t>
+  </si>
+  <si>
+    <t>YuzuLove_1</t>
+  </si>
+  <si>
+    <t>和柚茶约会2</t>
+  </si>
+  <si>
+    <t>获得遗物柚子茶的手柄，体力+10
+限定晚上</t>
+  </si>
+  <si>
+    <t>YuzuLove_2</t>
+  </si>
+  <si>
+    <t>和柚茶约会3</t>
+  </si>
+  <si>
+    <t>游戏力提升率+3%获得卡牌“专注模式”
+限定晚上</t>
+  </si>
+  <si>
+    <t>YuzuLove_3</t>
+  </si>
+  <si>
+    <t>和柚茶约会4</t>
+  </si>
+  <si>
+    <t>获得遗物柚子茶的枕头，体力+15
+限定晚上</t>
+  </si>
+  <si>
+    <t>YuzuLove_4</t>
+  </si>
+  <si>
+    <t>朋友聚会</t>
+  </si>
+  <si>
+    <t>消耗沪币降低压力，并且触发其他效果</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>Patry</t>
+  </si>
+  <si>
+    <t>阶段1结束——歌力</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“唱歌的心得”.歌力提升率+5%</t>
+  </si>
+  <si>
+    <t>phase_1_sing</t>
+  </si>
+  <si>
+    <t>阶段1结束——游戏力</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“游戏的心得”.游戏力提升率+5%</t>
+  </si>
+  <si>
+    <t>phase_1_game</t>
+  </si>
+  <si>
+    <t>阶段1结束——杂谈力</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“杂谈的心得”.杂谈力提升率+5%</t>
+  </si>
+  <si>
+    <t>phase_1_chat</t>
+  </si>
+  <si>
+    <t>阶段2结束——水友歌回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“唱歌的理论”.</t>
+  </si>
+  <si>
+    <t>phase_2_sing</t>
+  </si>
+  <si>
+    <t>阶段2结束——水友游戏回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“游戏的理论”.</t>
+  </si>
+  <si>
+    <t>phase_2_game</t>
+  </si>
+  <si>
+    <t>阶段2结束——视频鉴赏回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“杂谈的理论”.</t>
+  </si>
+  <si>
+    <t>phase_2_chat</t>
+  </si>
+  <si>
+    <t>阶段2结束——代抽回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“商店会员卡”.</t>
+  </si>
+  <si>
+    <t>phase_2_store</t>
+  </si>
+  <si>
+    <t>阶段3结束——水友投稿回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“爱墨生的投稿”.</t>
+  </si>
+  <si>
+    <t>phase_3_tougao</t>
+  </si>
+  <si>
+    <t>阶段3结束——生日回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“爱墨生的祝福”.</t>
+  </si>
+  <si>
+    <t>phase_3_shengri</t>
+  </si>
+  <si>
+    <t>阶段3结束——粉丝礼物回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“爱墨生的礼物”.</t>
+  </si>
+  <si>
+    <t>phase_3_fan</t>
+  </si>
+  <si>
+    <t>阶段3结束——健身环挑战回</t>
+  </si>
+  <si>
+    <t>粉丝+500.沪币+200.舰长+3
+获得“爱墨生的精气”.</t>
+  </si>
+  <si>
+    <t>phase_3_tili</t>
+  </si>
+  <si>
+    <t>结局——水火歌会</t>
+  </si>
+  <si>
+    <t>歌力+50,游戏力+50，杂谈力+50</t>
+  </si>
+  <si>
+    <t>end_game</t>
+  </si>
+  <si>
+    <t>结局——段位挑战回</t>
+  </si>
+  <si>
+    <t>结局——清楚聊天室</t>
+  </si>
+  <si>
+    <t>结局——人头麦回</t>
+  </si>
+  <si>
+    <t>结局——健身环耐久回</t>
+  </si>
+  <si>
+    <t>结局——百舰回</t>
+  </si>
+  <si>
+    <t>结局——新衣回嘉宾</t>
+  </si>
+  <si>
     <t>M卡</t>
   </si>
   <si>
@@ -905,6 +1396,12 @@
     <t>fun</t>
   </si>
   <si>
+    <t>营收</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
@@ -914,20 +1411,47 @@
     <t xml:space="preserve"> TargetValue</t>
   </si>
   <si>
-    <t>Stream,0,1</t>
-  </si>
-  <si>
-    <t>upgrade</t>
-  </si>
-  <si>
-    <t>VRaisingUpgradeSelectEffect</t>
+    <t>限定晚上</t>
+  </si>
+  <si>
+    <t>VTimeOfDayPlacingCondition</t>
+  </si>
+  <si>
+    <t>限定中午</t>
+  </si>
+  <si>
+    <t>限定早上</t>
+  </si>
+  <si>
+    <t>限定周1</t>
+  </si>
+  <si>
+    <t>VDayPlacingCondition</t>
+  </si>
+  <si>
+    <t>限定周2</t>
+  </si>
+  <si>
+    <t>限定周3</t>
+  </si>
+  <si>
+    <t>限定周4</t>
+  </si>
+  <si>
+    <t>限定周5</t>
+  </si>
+  <si>
+    <t>限定周6</t>
+  </si>
+  <si>
+    <t>限定周7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -936,22 +1460,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -994,7 +1505,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE5FD1F"/>
+        <fgColor rgb="FFA122FB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1023,7 +1534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1031,7 +1542,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1064,7 +1575,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1078,6 +1588,7 @@
       <color rgb="FFF567ED"/>
       <color rgb="FFDEBA2C"/>
       <color rgb="FFFD460D"/>
+      <color rgb="FFA122FB"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1349,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -1548,7 +2059,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1565,7 +2076,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1582,7 +2093,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1599,7 +2110,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1616,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1633,7 +2144,7 @@
         <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1725,14 +2236,8 @@
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
       <c r="D22" t="s">
         <v>49</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1740,16 +2245,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
         <v>49</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1757,16 +2256,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
         <v>51</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>52</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>53</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1774,13 +2273,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s">
         <v>55</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1788,19 +2287,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" t="s">
         <v>57</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>58</v>
       </c>
       <c r="E26">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1808,13 +2307,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
         <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1822,16 +2321,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1839,16 +2338,16 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
         <v>58</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1859,7 +2358,7 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1879,7 +2378,7 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1899,7 +2398,7 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1916,10 +2415,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s">
         <v>65</v>
-      </c>
-      <c r="D33" t="s">
-        <v>66</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1930,10 +2429,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -1944,10 +2443,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -1958,10 +2457,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F36">
         <v>3</v>
@@ -1972,10 +2471,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F37">
         <v>4</v>
@@ -1986,16 +2485,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" t="s">
         <v>58</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2003,10 +2502,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" t="s">
         <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2014,16 +2513,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2031,16 +2530,16 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2048,13 +2547,16 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="E42">
+        <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2062,13 +2564,16 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2076,14 +2581,277 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>272</v>
+        <v>78</v>
+      </c>
+      <c r="D44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="D49" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F57" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>103</v>
+      </c>
+      <c r="D59" t="s">
+        <v>104</v>
+      </c>
+      <c r="F59" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" t="s">
+        <v>104</v>
+      </c>
+      <c r="F60" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" t="s">
+        <v>104</v>
+      </c>
+      <c r="F61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>110</v>
+      </c>
+      <c r="D62" t="s">
+        <v>104</v>
+      </c>
+      <c r="F62" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -2127,61 +2895,61 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="I1" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="N1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="O1" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="P1" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="Q1" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="R1" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="T1" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="U1" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="V1" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="W1" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -2189,31 +2957,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K2" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -2231,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="R2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S2">
         <v>7</v>
       </c>
       <c r="T2">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -2248,31 +3016,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K3" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -2290,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="R3">
         <v>6</v>
@@ -2299,7 +3067,7 @@
         <v>7</v>
       </c>
       <c r="T3">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -2307,31 +3075,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K4" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -2349,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="R4">
         <v>6</v>
@@ -2358,7 +3126,7 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -2366,31 +3134,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K5" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -2408,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="R5" s="1">
         <v>6</v>
@@ -2417,7 +3185,7 @@
         <v>7</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -2425,40 +3193,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K6" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L6">
         <v>10</v>
       </c>
       <c r="M6">
-        <v>150</v>
+        <v>8000</v>
       </c>
       <c r="N6">
-        <v>300</v>
+        <v>6000</v>
       </c>
       <c r="O6">
         <v>50</v>
@@ -2467,19 +3235,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="R6" s="1">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="S6" s="13">
         <v>20</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="U6" t="s">
-        <v>270</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2487,37 +3255,37 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K7" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L7">
         <v>10</v>
       </c>
       <c r="M7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="N7">
         <v>6000</v>
@@ -2529,19 +3297,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="R7" s="1">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="S7" s="13">
         <v>20</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="U7" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -2549,37 +3317,37 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K8" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L8">
         <v>10</v>
       </c>
       <c r="M8">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="N8">
         <v>6000</v>
@@ -2591,19 +3359,19 @@
         <v>2</v>
       </c>
       <c r="Q8" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="R8" s="1">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="S8" s="13">
         <v>20</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="U8" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -2611,58 +3379,61 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K9" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L9">
         <v>12</v>
       </c>
       <c r="M9">
-        <v>42000</v>
+        <v>12000</v>
       </c>
       <c r="N9">
         <v>22000</v>
       </c>
       <c r="O9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="R9">
         <v>6</v>
       </c>
       <c r="S9" s="13">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T9">
         <v>100</v>
+      </c>
+      <c r="U9" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -2670,58 +3441,61 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L10">
         <v>12</v>
       </c>
       <c r="M10">
-        <v>42000</v>
+        <v>12000</v>
       </c>
       <c r="N10">
         <v>22000</v>
       </c>
       <c r="O10">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P10">
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="R10">
         <v>6</v>
       </c>
       <c r="S10" s="13">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T10">
         <v>100</v>
+      </c>
+      <c r="U10" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -2729,58 +3503,61 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L11">
         <v>12</v>
       </c>
       <c r="M11">
-        <v>42000</v>
+        <v>12000</v>
       </c>
       <c r="N11">
         <v>22000</v>
       </c>
       <c r="O11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="R11">
         <v>6</v>
       </c>
-      <c r="S11">
-        <v>7</v>
+      <c r="S11" s="13">
+        <v>20</v>
       </c>
       <c r="T11">
         <v>100</v>
+      </c>
+      <c r="U11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -2788,117 +3565,123 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K12" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L12">
         <v>12</v>
       </c>
       <c r="M12">
-        <v>42000</v>
+        <v>12000</v>
       </c>
       <c r="N12">
         <v>22000</v>
       </c>
       <c r="O12">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>2</v>
       </c>
       <c r="Q12" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="R12">
         <v>6</v>
       </c>
-      <c r="S12">
-        <v>7</v>
+      <c r="S12" s="13">
+        <v>20</v>
       </c>
       <c r="T12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:23">
+      <c r="U12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15.95" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" t="s">
         <v>136</v>
-      </c>
-      <c r="C13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K13" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L13">
         <v>12</v>
       </c>
       <c r="M13">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="N13">
         <v>30000</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P13">
         <v>2</v>
       </c>
       <c r="Q13" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="R13">
         <v>6</v>
       </c>
-      <c r="S13">
-        <v>7</v>
+      <c r="S13" s="13">
+        <v>20</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="U13" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -2906,58 +3689,61 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K14" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L14">
         <v>12</v>
       </c>
       <c r="M14">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="N14">
         <v>30000</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="R14">
         <v>6</v>
       </c>
-      <c r="S14">
-        <v>7</v>
+      <c r="S14" s="13">
+        <v>20</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="U14" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -2965,58 +3751,61 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K15" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L15">
         <v>12</v>
       </c>
       <c r="M15">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="N15">
         <v>30000</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="R15">
         <v>6</v>
       </c>
-      <c r="S15">
-        <v>7</v>
+      <c r="S15" s="13">
+        <v>20</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="U15" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -3024,483 +3813,510 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K16" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L16">
         <v>12</v>
       </c>
       <c r="M16">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="N16">
         <v>30000</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P16">
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="R16">
         <v>6</v>
       </c>
-      <c r="S16">
-        <v>7</v>
+      <c r="S16" s="13">
+        <v>20</v>
       </c>
       <c r="T16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>120</v>
+      </c>
+      <c r="U16" t="s">
+        <v>190</v>
+      </c>
+      <c r="V16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K17" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L17">
         <v>15</v>
       </c>
       <c r="M17">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N17">
         <v>50000</v>
       </c>
       <c r="O17">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="R17">
         <v>6</v>
       </c>
-      <c r="S17">
-        <v>7</v>
+      <c r="S17" s="13">
+        <v>20</v>
       </c>
       <c r="T17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>140</v>
+      </c>
+      <c r="U17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K18" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L18">
         <v>15</v>
       </c>
       <c r="M18">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N18">
         <v>50000</v>
       </c>
       <c r="O18">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P18">
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="R18">
         <v>6</v>
       </c>
-      <c r="S18">
-        <v>7</v>
+      <c r="S18" s="13">
+        <v>20</v>
       </c>
       <c r="T18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>140</v>
+      </c>
+      <c r="U18" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K19" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L19">
         <v>15</v>
       </c>
       <c r="M19">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N19">
         <v>50000</v>
       </c>
       <c r="O19">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P19">
         <v>2</v>
       </c>
       <c r="Q19" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="R19">
         <v>6</v>
       </c>
-      <c r="S19">
-        <v>7</v>
+      <c r="S19" s="13">
+        <v>20</v>
       </c>
       <c r="T19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>140</v>
+      </c>
+      <c r="U19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L20">
         <v>15</v>
       </c>
       <c r="M20">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N20">
         <v>50000</v>
       </c>
       <c r="O20">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="R20">
         <v>6</v>
       </c>
-      <c r="S20">
-        <v>7</v>
+      <c r="S20" s="13">
+        <v>20</v>
       </c>
       <c r="T20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>140</v>
+      </c>
+      <c r="U20" t="s">
+        <v>155</v>
+      </c>
+      <c r="V20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K21" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L21">
         <v>15</v>
       </c>
       <c r="M21">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N21">
         <v>50000</v>
       </c>
       <c r="O21">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P21">
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>161</v>
+        <v>210</v>
       </c>
       <c r="R21">
         <v>6</v>
       </c>
-      <c r="S21">
-        <v>7</v>
+      <c r="S21" s="13">
+        <v>20</v>
       </c>
       <c r="T21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>140</v>
+      </c>
+      <c r="U21" t="s">
+        <v>159</v>
+      </c>
+      <c r="V21" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="C22" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K22" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L22">
         <v>15</v>
       </c>
       <c r="M22">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N22">
         <v>50000</v>
       </c>
       <c r="O22">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="R22">
         <v>6</v>
       </c>
-      <c r="S22">
-        <v>7</v>
+      <c r="S22" s="13">
+        <v>20</v>
       </c>
       <c r="T22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="C23" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K23" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L23">
         <v>15</v>
       </c>
       <c r="M23">
-        <v>140000</v>
+        <v>31000</v>
       </c>
       <c r="N23">
         <v>50000</v>
       </c>
       <c r="O23">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="P23">
         <v>2</v>
       </c>
       <c r="Q23" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="R23">
         <v>6</v>
       </c>
-      <c r="S23">
-        <v>7</v>
+      <c r="S23" s="13">
+        <v>20</v>
       </c>
       <c r="T23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:22">
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:22">
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:22">
       <c r="R27" s="1"/>
     </row>
   </sheetData>
@@ -3510,7 +4326,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
@@ -3540,25 +4356,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
@@ -3566,31 +4382,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>219</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
@@ -3598,31 +4414,31 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>54</v>
+        <v>223</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
@@ -3630,31 +4446,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>175</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
@@ -3662,31 +4478,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="33" customHeight="1">
@@ -3694,31 +4510,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>181</v>
+        <v>235</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>182</v>
+        <v>236</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>183</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -3726,31 +4542,31 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>178</v>
+        <v>232</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
@@ -3758,31 +4574,31 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
@@ -3790,31 +4606,31 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
@@ -3822,31 +4638,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
@@ -3854,31 +4670,31 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
@@ -3886,31 +4702,31 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
@@ -3918,31 +4734,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
@@ -3950,31 +4766,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>207</v>
+        <v>261</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>208</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
@@ -3982,28 +4798,31 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>212</v>
+        <v>266</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="42" customHeight="1">
@@ -4011,31 +4830,29 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
@@ -4043,31 +4860,29 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>217</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
@@ -4075,31 +4890,29 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>214</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
@@ -4107,28 +4920,31 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G19" s="1">
+        <v>9</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G19" s="1">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="I19" s="4" t="s">
-        <v>102</v>
+        <v>139</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
@@ -4136,28 +4952,31 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G20" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>54</v>
+        <v>223</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>106</v>
+        <v>144</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
@@ -4165,28 +4984,31 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G21" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>54</v>
+        <v>227</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>109</v>
+        <v>148</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
@@ -4194,31 +5016,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>227</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
@@ -4226,31 +5048,31 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
@@ -4258,31 +5080,31 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
+        <v>289</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
@@ -4290,31 +5112,31 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
+        <v>292</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
@@ -4322,31 +5144,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
@@ -4354,31 +5176,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
@@ -4386,31 +5208,31 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>241</v>
+        <v>303</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
@@ -4418,31 +5240,31 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1">
@@ -4450,31 +5272,31 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>246</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="30" customHeight="1">
@@ -4482,28 +5304,28 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>247</v>
+        <v>313</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1">
@@ -4511,25 +5333,1323 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>248</v>
+        <v>314</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>101</v>
+        <v>316</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>212</v>
+        <v>266</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="30" customHeight="1">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="30" customHeight="1">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="30" customHeight="1">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="30" customHeight="1">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" s="1">
+        <v>5</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="30" customHeight="1">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="30" customHeight="1">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="30" customHeight="1">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="30" customHeight="1">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="30" customHeight="1">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="30" customHeight="1">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="30" customHeight="1">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="1">
+        <v>5</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="30" customHeight="1">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="1">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="30" customHeight="1">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G45" s="1">
+        <v>5</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="30" customHeight="1">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" s="1">
+        <v>5</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="30" customHeight="1">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G47" s="1">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="30" customHeight="1">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G48" s="1">
+        <v>5</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="30" customHeight="1">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="1">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="30" customHeight="1">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G50" s="1">
+        <v>5</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="J50" s="1">
+        <v>3</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="30" customHeight="1">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G51" s="1">
+        <v>5</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="J51" s="1">
+        <v>3</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="30" customHeight="1">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G52" s="1">
+        <v>5</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="J52" s="1">
+        <v>3</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="30" customHeight="1">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="J53" s="1">
+        <v>3</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="30" customHeight="1">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E54" s="1">
+        <v>3</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G54" s="1">
+        <v>80</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="30" customHeight="1">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="30" customHeight="1">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="45">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="30" customHeight="1">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="30" customHeight="1">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="30" customHeight="1">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="30" customHeight="1">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="30" customHeight="1">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="30" customHeight="1">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="30" customHeight="1">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -4539,7 +6659,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4571,13 +6691,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>429</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4585,13 +6705,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>432</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4599,13 +6719,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>434</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>254</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4613,13 +6733,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>436</v>
       </c>
       <c r="D5" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
       <c r="E5" t="s">
-        <v>256</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4627,13 +6747,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>437</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
       <c r="E6" t="s">
-        <v>257</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4641,13 +6761,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>438</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>439</v>
       </c>
       <c r="E7" t="s">
-        <v>260</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4655,13 +6775,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>438</v>
       </c>
       <c r="D8" t="s">
-        <v>259</v>
+        <v>439</v>
       </c>
       <c r="E8" t="s">
-        <v>261</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4669,13 +6789,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>442</v>
       </c>
       <c r="D9" t="s">
-        <v>263</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
-        <v>264</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4683,13 +6803,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>265</v>
+        <v>445</v>
       </c>
       <c r="D10" t="s">
-        <v>263</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
-        <v>266</v>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>447</v>
+      </c>
+      <c r="D11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E11" t="s">
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -4699,7 +6833,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.140625" customWidth="1"/>
@@ -4714,16 +6848,156 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>267</v>
+        <v>449</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>268</v>
+        <v>450</v>
       </c>
       <c r="E1" t="s">
-        <v>269</v>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D4" t="s">
+        <v>453</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D6" t="s">
+        <v>457</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" t="s">
+        <v>457</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>460</v>
+      </c>
+      <c r="D8" t="s">
+        <v>457</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9" t="s">
+        <v>457</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>462</v>
+      </c>
+      <c r="D10" t="s">
+        <v>457</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>463</v>
+      </c>
+      <c r="D11" t="s">
+        <v>457</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70553E5D-D106-4EE7-9BC2-538369BC8EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD8A882-F706-47C4-A2BF-C956EA3E44A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -3223,7 +3223,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>8000</v>
+        <v>20</v>
       </c>
       <c r="N6">
         <v>6000</v>
@@ -3285,7 +3285,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>8000</v>
+        <v>20</v>
       </c>
       <c r="N7">
         <v>6000</v>
@@ -3347,7 +3347,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>8000</v>
+        <v>20</v>
       </c>
       <c r="N8">
         <v>6000</v>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD8A882-F706-47C4-A2BF-C956EA3E44A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0429C6D9-B5DE-45CB-90CD-BE772E98CFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -5933,7 +5933,7 @@
         <v>298</v>
       </c>
       <c r="J50" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>373</v>
@@ -5968,7 +5968,7 @@
         <v>298</v>
       </c>
       <c r="J51" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>376</v>
@@ -6003,7 +6003,7 @@
         <v>298</v>
       </c>
       <c r="J52" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>379</v>
@@ -6038,7 +6038,7 @@
         <v>298</v>
       </c>
       <c r="J53" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>382</v>

--- a/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
+++ b/Assets/StreamingAssets/Configurations/dev/Raising.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0429C6D9-B5DE-45CB-90CD-BE772E98CFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E54035-57F8-4007-B922-7A4AB48A7499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RaisingEffects" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="DialogueEvents" sheetId="4" r:id="rId3"/>
     <sheet name="CardConditions" sheetId="2" r:id="rId4"/>
     <sheet name="PlacingConditions" sheetId="6" r:id="rId5"/>
+    <sheet name="SchedulingConditions" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$S$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StreamEvents!$A$1:$T$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="480">
   <si>
     <t>ID</t>
   </si>
@@ -307,7 +308,7 @@
     <t>获得一张高稀有卡牌获得</t>
   </si>
   <si>
-    <t>0,0,1,0,0,0</t>
+    <t>0,0.8,0.2,0,0,0</t>
   </si>
   <si>
     <t>小室好感升级</t>
@@ -388,6 +389,18 @@
     <t>CAChattingAbility,CAFollowerCount</t>
   </si>
   <si>
+    <t>强化一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingUpgradeSelectEffect</t>
+  </si>
+  <si>
+    <t>随机获得一张卡牌</t>
+  </si>
+  <si>
+    <t>VRaisingAddRandomCardEffect</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -694,7 +707,7 @@
     <t>声乐练习</t>
   </si>
   <si>
-    <t>歌力+18</t>
+    <t>&lt;sprite name=Icon_SingingAbility&gt;歌力+18</t>
   </si>
   <si>
     <t>singpractice</t>
@@ -706,7 +719,7 @@
     <t>游戏练习</t>
   </si>
   <si>
-    <t>游戏力+18</t>
+    <t>&lt;sprite name=Icon_GamingAbility&gt;游戏力+18</t>
   </si>
   <si>
     <t>gamepractice</t>
@@ -718,7 +731,7 @@
     <t>对话练习</t>
   </si>
   <si>
-    <t>杂谈力+18</t>
+    <t>&lt;sprite name=Icon_ChattingAbility&gt;杂谈力杂谈力+18</t>
   </si>
   <si>
     <t>chatpractice</t>
@@ -727,10 +740,10 @@
     <t>ChatPractice</t>
   </si>
   <si>
-    <t>小憩一会</t>
-  </si>
-  <si>
-    <t>体力+15</t>
+    <t>小睡一会</t>
+  </si>
+  <si>
+    <t>&lt;sprite name=Icon_Stamina&gt;体力+15</t>
   </si>
   <si>
     <t>Rest</t>
@@ -748,7 +761,7 @@
     <t>睡个大的</t>
   </si>
   <si>
-    <t>体力+35，随机删除一张基础牌</t>
+    <t>&lt;sprite name=Icon_Stamina&gt;体力+35，选择一张卡牌删除</t>
   </si>
   <si>
     <t>Sleep</t>
@@ -757,7 +770,7 @@
     <t>放一天假</t>
   </si>
   <si>
-    <t>体力+70,从卡组中选择一张卡牌删除</t>
+    <t>&lt;sprite name=Icon_Stamina&gt;体力+70,从卡组中选择一张卡牌删除</t>
   </si>
   <si>
     <t>Dayoff</t>
@@ -766,7 +779,7 @@
     <t>直播成功</t>
   </si>
   <si>
-    <t>粉丝+200，金钱+30，舰长+1，获得一张卡</t>
+    <t>&lt;sprite name=Icon_Follower&gt;+200，金钱+30，&lt;sprite name=Icon_Membership&gt;&lt;sprite name=Icon_Membership&gt;舰长+1，获得一张卡</t>
   </si>
   <si>
     <t>Other</t>
@@ -808,7 +821,7 @@
     <t>兼职</t>
   </si>
   <si>
-    <t>获得沪币，并且触发其他效果</t>
+    <t>获得&lt;sprite name=Icon_Money&gt;沪币，并触发随机构筑卡牌的效果</t>
   </si>
   <si>
     <t>Work</t>
@@ -823,7 +836,7 @@
     <t>剪辑切片</t>
   </si>
   <si>
-    <t>获得沪币，并且选择卡牌获得</t>
+    <t>定向获得卡牌</t>
   </si>
   <si>
     <t>Work2</t>
@@ -862,7 +875,7 @@
     <t>进阶唱歌练习</t>
   </si>
   <si>
-    <t>歌力+25</t>
+    <t>&lt;sprite name=Icon_SingingAbility&gt;歌力+25</t>
   </si>
   <si>
     <t>SingPractice2</t>
@@ -871,7 +884,7 @@
     <t>进阶游戏练习</t>
   </si>
   <si>
-    <t>游戏力+25</t>
+    <t>&lt;sprite name=Icon_GamingAbility&gt;游戏力+25</t>
   </si>
   <si>
     <t>GamePractice2</t>
@@ -880,7 +893,7 @@
     <t>进阶杂谈练习</t>
   </si>
   <si>
-    <t>杂谈力+25</t>
+    <t>&lt;sprite name=Icon_ChattingAbility&gt;杂谈力+25</t>
   </si>
   <si>
     <t>ChatPractice2</t>
@@ -925,7 +938,7 @@
     <t>找血王喝酒</t>
   </si>
   <si>
-    <t>至尊血王好感度+5</t>
+    <t>至尊血王&lt;sprite name=love&gt;好感度+5</t>
   </si>
   <si>
     <t>Coop</t>
@@ -943,7 +956,7 @@
     <t>找小室玩</t>
   </si>
   <si>
-    <t>小室好感度+5</t>
+    <t>小室&lt;sprite name=love&gt;好感度+5</t>
   </si>
   <si>
     <t>XiaoShiMeet1</t>
@@ -952,7 +965,7 @@
     <t>和井井练歌</t>
   </si>
   <si>
-    <t>井井好感度+5</t>
+    <t>井井&lt;sprite name=love&gt;好感度+5</t>
   </si>
   <si>
     <t>##Meet1</t>
@@ -961,7 +974,7 @@
     <t>和柚茶打游戏</t>
   </si>
   <si>
-    <t>柚子茶好感度+5</t>
+    <t>柚子茶&lt;sprite name=love&gt;好感度+5</t>
   </si>
   <si>
     <t>YuzuMeet1</t>
@@ -970,7 +983,7 @@
     <t>和糯糯聊天</t>
   </si>
   <si>
-    <t>画师mama好感度+5</t>
+    <t>画师mama&lt;sprite name=love&gt;好感度+5</t>
   </si>
   <si>
     <t>MamaMeet1</t>
@@ -979,13 +992,13 @@
     <t>大白猫好感度增加事件</t>
   </si>
   <si>
-    <t>大白猫好感度+5</t>
+    <t>大白猫&lt;sprite name=love&gt;好感度+5</t>
   </si>
   <si>
     <t>外出吃饭</t>
   </si>
   <si>
-    <t>消耗沪币回复体力，并且触发其他效果</t>
+    <t>消耗&lt;sprite name=Icon_Money&gt;沪币回复&lt;sprite name=Icon_Stamina&gt;体力，并且触发其他效果</t>
   </si>
   <si>
     <t>Money</t>
@@ -1000,7 +1013,7 @@
     <t>动态营业</t>
   </si>
   <si>
-    <t>获得粉丝，并且触发其他效果</t>
+    <t>获得&lt;sprite name=Icon_Follower&gt;粉丝，并且触发其他效果</t>
   </si>
   <si>
     <t>Work3</t>
@@ -1009,7 +1022,7 @@
     <t>和小室约会1</t>
   </si>
   <si>
-    <t>最大体力值+5，粉丝+300</t>
+    <t>最大&lt;sprite name=Icon_Stamina&gt;体力值+5，&lt;sprite name=Icon_Follower&gt;+300</t>
   </si>
   <si>
     <t>deeplove</t>
@@ -1021,7 +1034,7 @@
     <t>和小室约会2</t>
   </si>
   <si>
-    <t>获得遗物小室的头绳，回复10点体力</t>
+    <t>获得小室的头绳，回复10点&lt;sprite name=Icon_Stamina&gt;体力</t>
   </si>
   <si>
     <t>XiaoShiLove_2</t>
@@ -1030,7 +1043,7 @@
     <t>和小室约会3</t>
   </si>
   <si>
-    <t>最大体力值+5，选择一张高稀有度卡获得</t>
+    <t>最大&lt;sprite name=Icon_Stamina&gt;体力值+5，选择一张高稀有度卡获得</t>
   </si>
   <si>
     <t>XiaoShiLove_3</t>
@@ -1039,7 +1052,7 @@
     <t>和小室约会4</t>
   </si>
   <si>
-    <t>获得遗物小室的玫瑰，回复15点体力</t>
+    <t>获得小室的玫瑰，回复15点&lt;sprite name=Icon_Stamina&gt;体力</t>
   </si>
   <si>
     <t>XiaoShiLove_4</t>
@@ -1057,7 +1070,7 @@
     <t>和血王约会2</t>
   </si>
   <si>
-    <t>获得遗物雪王的狗，随机强化一张卡</t>
+    <t>获得雪王的狗，随机强化一张卡</t>
   </si>
   <si>
     <t>XuewangLove_2</t>
@@ -1075,7 +1088,7 @@
     <t>和血王约会4</t>
   </si>
   <si>
-    <t>获得遗物雪王的心脏，压力-1</t>
+    <t>获得雪王的心脏，压力-1</t>
   </si>
   <si>
     <t>XuewangLove_4</t>
@@ -1093,7 +1106,7 @@
     <t>和井井约会2</t>
   </si>
   <si>
-    <t>获得遗物井井的麦克风，粉丝+200</t>
+    <t>获得井井的麦克风，&lt;sprite name=Icon_Follower&gt;+200</t>
   </si>
   <si>
     <t>##Love_2</t>
@@ -1111,7 +1124,7 @@
     <t>和井井约会4</t>
   </si>
   <si>
-    <t>获得遗物井井的光环，粉丝+300</t>
+    <t>获得井井的光环，&lt;sprite name=Icon_Follower&gt;+300</t>
   </si>
   <si>
     <t>##Love_4</t>
@@ -1120,7 +1133,7 @@
     <t>和糯糯约会1</t>
   </si>
   <si>
-    <t>舰长+5，粉丝+200，获得卡牌“工作音”</t>
+    <t>&lt;sprite name=Icon_Membership&gt;&lt;sprite name=Icon_Membership&gt;舰长+5，&lt;sprite name=Icon_Follower&gt;+200，获得卡牌“工作音”</t>
   </si>
   <si>
     <t>MamaLove_1</t>
@@ -1129,7 +1142,7 @@
     <t>和糯糯约会2</t>
   </si>
   <si>
-    <t>获得遗物糯糯的画笔，沪币+50</t>
+    <t>获得糯糯的画笔，&lt;sprite name=Icon_Money&gt;沪币+50</t>
   </si>
   <si>
     <t>MamaLove_2</t>
@@ -1138,7 +1151,7 @@
     <t>和糯糯约会3</t>
   </si>
   <si>
-    <t>舰长+10，粉丝+300，获得卡牌“摸鱼”</t>
+    <t>&lt;sprite name=Icon_Membership&gt;&lt;sprite name=Icon_Membership&gt;舰长+10，&lt;sprite name=Icon_Follower&gt;+300，获得卡牌“摸鱼”</t>
   </si>
   <si>
     <t>MamaLove_3</t>
@@ -1147,7 +1160,7 @@
     <t>和糯糯约会4</t>
   </si>
   <si>
-    <t>获得遗物糯糯的画板，沪币+200</t>
+    <t>获得糯糯的画板，&lt;sprite name=Icon_Money&gt;沪币+200</t>
   </si>
   <si>
     <t>MamaLove_4</t>
@@ -1166,7 +1179,7 @@
     <t>和柚茶约会2</t>
   </si>
   <si>
-    <t>获得遗物柚子茶的手柄，体力+10
+    <t>获得柚子茶的手柄，&lt;sprite name=Icon_Stamina&gt;体力+10
 限定晚上</t>
   </si>
   <si>
@@ -1186,29 +1199,29 @@
     <t>和柚茶约会4</t>
   </si>
   <si>
-    <t>获得遗物柚子茶的枕头，体力+15
+    <t>获得柚子茶的枕头，&lt;sprite name=Icon_Stamina&gt;体力+15
 限定晚上</t>
   </si>
   <si>
     <t>YuzuLove_4</t>
   </si>
   <si>
-    <t>朋友聚会</t>
-  </si>
-  <si>
-    <t>消耗沪币降低压力，并且触发其他效果</t>
+    <t>开趴</t>
+  </si>
+  <si>
+    <t>强化卡牌并获得属性</t>
   </si>
   <si>
     <t>party</t>
   </si>
   <si>
-    <t>Patry</t>
+    <t>Party</t>
   </si>
   <si>
     <t>阶段1结束——歌力</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“唱歌的心得”.歌力提升率+5%</t>
   </si>
   <si>
@@ -1218,7 +1231,7 @@
     <t>阶段1结束——游戏力</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“游戏的心得”.游戏力提升率+5%</t>
   </si>
   <si>
@@ -1228,7 +1241,7 @@
     <t>阶段1结束——杂谈力</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“杂谈的心得”.杂谈力提升率+5%</t>
   </si>
   <si>
@@ -1238,8 +1251,8 @@
     <t>阶段2结束——水友歌回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
-获得“唱歌的理论”.</t>
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
+获得“唱歌的理论”.歌力提升率+5%</t>
   </si>
   <si>
     <t>phase_2_sing</t>
@@ -1248,8 +1261,8 @@
     <t>阶段2结束——水友游戏回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
-获得“游戏的理论”.</t>
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
+获得“游戏的理论”.游戏力提升率+5%</t>
   </si>
   <si>
     <t>phase_2_game</t>
@@ -1258,8 +1271,8 @@
     <t>阶段2结束——视频鉴赏回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
-获得“杂谈的理论”.</t>
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
+获得“杂谈的理论”.杂谈力提升率+5%</t>
   </si>
   <si>
     <t>phase_2_chat</t>
@@ -1268,8 +1281,8 @@
     <t>阶段2结束——代抽回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
-获得“商店会员卡”.</t>
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
+获得“商店会员卡”.三种属性提升率增加3%</t>
   </si>
   <si>
     <t>phase_2_store</t>
@@ -1278,7 +1291,7 @@
     <t>阶段3结束——水友投稿回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“爱墨生的投稿”.</t>
   </si>
   <si>
@@ -1288,7 +1301,7 @@
     <t>阶段3结束——生日回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“爱墨生的祝福”.</t>
   </si>
   <si>
@@ -1298,7 +1311,7 @@
     <t>阶段3结束——粉丝礼物回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“爱墨生的礼物”.</t>
   </si>
   <si>
@@ -1308,7 +1321,7 @@
     <t>阶段3结束——健身环挑战回</t>
   </si>
   <si>
-    <t>粉丝+500.沪币+200.舰长+3
+    <t>&lt;sprite name=Icon_Follower&gt;+500.&lt;sprite name=Icon_Money&gt;沪币+200.&lt;sprite name=Icon_Membership&gt;舰长+3
 获得“爱墨生的精气”.</t>
   </si>
   <si>
@@ -1318,7 +1331,7 @@
     <t>结局——水火歌会</t>
   </si>
   <si>
-    <t>歌力+50,游戏力+50，杂谈力+50</t>
+    <t>&lt;sprite name=Icon_SingingAbility&gt;歌力+50,&lt;sprite name=Icon_GamingAbility&gt;游戏力+50，&lt;sprite name=Icon_ChattingAbility&gt;杂谈力+50</t>
   </si>
   <si>
     <t>end_game</t>
@@ -1445,6 +1458,42 @@
   </si>
   <si>
     <t>限定周7</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>TargetType</t>
+  </si>
+  <si>
+    <t>Effect1</t>
+  </si>
+  <si>
+    <t>E1Param</t>
+  </si>
+  <si>
+    <t>Effect2</t>
+  </si>
+  <si>
+    <t>E2Param</t>
+  </si>
+  <si>
+    <t>Effect3</t>
+  </si>
+  <si>
+    <t>E3Param</t>
+  </si>
+  <si>
+    <t>SchedulingCondition</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>UDLR</t>
   </si>
 </sst>
 </file>
@@ -1522,9 +1571,18 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -1534,7 +1592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1575,6 +1633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1860,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -2849,6 +2908,31 @@
         <v>115</v>
       </c>
     </row>
+    <row r="65" spans="1:6">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>116</v>
+      </c>
+      <c r="D65" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>118</v>
+      </c>
+      <c r="D66" t="s">
+        <v>119</v>
+      </c>
+      <c r="F66" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2857,7 +2941,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -2867,21 +2951,21 @@
     <col min="5" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="9" max="9" width="8.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="12" width="3.28515625" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" customWidth="1"/>
-    <col min="18" max="18" width="8.28515625" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" customWidth="1"/>
-    <col min="20" max="20" width="14.140625" customWidth="1"/>
-    <col min="21" max="21" width="10.28515625" customWidth="1"/>
+    <col min="10" max="11" width="15.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="3.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" customWidth="1"/>
+    <col min="20" max="20" width="10.140625" customWidth="1"/>
+    <col min="21" max="21" width="14.140625" customWidth="1"/>
+    <col min="22" max="22" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2895,1438 +2979,1442 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>122</v>
+        <v>477</v>
       </c>
       <c r="L1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="P1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="R1" t="s">
-        <v>129</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="T1" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="S1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="U1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="V1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="W1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23">
+        <v>137</v>
+      </c>
+      <c r="X1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L2">
+        <v>143</v>
+      </c>
+      <c r="L2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M2">
         <v>8</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>100</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>200</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>10</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="R2">
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="S2">
         <v>6</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>7</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L3" t="s">
         <v>144</v>
       </c>
-      <c r="K3" t="s">
-        <v>140</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>478</v>
+      </c>
+      <c r="N3">
         <v>100</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>200</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>10</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>1</v>
       </c>
-      <c r="Q3" t="s">
-        <v>145</v>
-      </c>
-      <c r="R3">
+      <c r="R3" t="s">
+        <v>149</v>
+      </c>
+      <c r="S3">
         <v>6</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>7</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K4" t="s">
-        <v>140</v>
-      </c>
-      <c r="L4">
+        <v>152</v>
+      </c>
+      <c r="L4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M4">
         <v>8</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>100</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>200</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>10</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>2</v>
       </c>
-      <c r="Q4" t="s">
-        <v>149</v>
-      </c>
-      <c r="R4">
+      <c r="R4" t="s">
+        <v>153</v>
+      </c>
+      <c r="S4">
         <v>6</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>7</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K5" t="s">
-        <v>140</v>
-      </c>
-      <c r="L5">
+        <v>143</v>
+      </c>
+      <c r="L5" t="s">
+        <v>144</v>
+      </c>
+      <c r="M5">
         <v>10</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>200</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>300</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>25</v>
       </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>151</v>
-      </c>
-      <c r="R5" s="1">
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>155</v>
+      </c>
+      <c r="S5" s="1">
         <v>6</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>7</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K6" t="s">
-        <v>140</v>
-      </c>
-      <c r="L6">
+        <v>143</v>
+      </c>
+      <c r="L6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="M6">
+      <c r="N6">
+        <v>800</v>
+      </c>
+      <c r="O6">
+        <v>6000</v>
+      </c>
+      <c r="P6">
+        <v>50</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>158</v>
+      </c>
+      <c r="S6" s="1">
+        <v>53</v>
+      </c>
+      <c r="T6" s="13">
         <v>20</v>
       </c>
-      <c r="N6">
-        <v>6000</v>
-      </c>
-      <c r="O6">
-        <v>50</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>154</v>
-      </c>
-      <c r="R6" s="1">
-        <v>53</v>
-      </c>
-      <c r="S6" s="13">
-        <v>20</v>
-      </c>
-      <c r="T6">
+      <c r="U6">
         <v>60</v>
       </c>
-      <c r="U6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
+      <c r="V6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L7" t="s">
         <v>144</v>
       </c>
-      <c r="K7" t="s">
-        <v>140</v>
-      </c>
-      <c r="L7">
+      <c r="M7">
         <v>10</v>
       </c>
-      <c r="M7">
+      <c r="N7">
+        <v>800</v>
+      </c>
+      <c r="O7">
+        <v>6000</v>
+      </c>
+      <c r="P7">
+        <v>50</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>162</v>
+      </c>
+      <c r="S7" s="1">
+        <v>54</v>
+      </c>
+      <c r="T7" s="13">
         <v>20</v>
       </c>
-      <c r="N7">
-        <v>6000</v>
-      </c>
-      <c r="O7">
-        <v>50</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R7" s="1">
-        <v>54</v>
-      </c>
-      <c r="S7" s="13">
-        <v>20</v>
-      </c>
-      <c r="T7">
+      <c r="U7">
         <v>60</v>
       </c>
-      <c r="U7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
+      <c r="V7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K8" t="s">
-        <v>140</v>
-      </c>
-      <c r="L8">
+        <v>152</v>
+      </c>
+      <c r="L8" t="s">
+        <v>144</v>
+      </c>
+      <c r="M8">
         <v>10</v>
       </c>
-      <c r="M8">
+      <c r="N8">
+        <v>800</v>
+      </c>
+      <c r="O8">
+        <v>6000</v>
+      </c>
+      <c r="P8">
+        <v>50</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8" t="s">
+        <v>166</v>
+      </c>
+      <c r="S8" s="1">
+        <v>55</v>
+      </c>
+      <c r="T8" s="13">
         <v>20</v>
       </c>
-      <c r="N8">
-        <v>6000</v>
-      </c>
-      <c r="O8">
-        <v>50</v>
-      </c>
-      <c r="P8">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>162</v>
-      </c>
-      <c r="R8" s="1">
-        <v>55</v>
-      </c>
-      <c r="S8" s="13">
-        <v>20</v>
-      </c>
-      <c r="T8">
+      <c r="U8">
         <v>60</v>
       </c>
-      <c r="U8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
+      <c r="V8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K9" t="s">
-        <v>140</v>
-      </c>
-      <c r="L9">
+        <v>143</v>
+      </c>
+      <c r="L9" t="s">
+        <v>144</v>
+      </c>
+      <c r="M9">
         <v>12</v>
       </c>
-      <c r="M9">
-        <v>12000</v>
-      </c>
       <c r="N9">
+        <v>1500</v>
+      </c>
+      <c r="O9">
         <v>22000</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>100</v>
       </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>166</v>
-      </c>
-      <c r="R9">
-        <v>6</v>
-      </c>
-      <c r="S9" s="13">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>170</v>
+      </c>
+      <c r="S9" s="1">
+        <v>56</v>
+      </c>
+      <c r="T9" s="13">
         <v>20</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>100</v>
       </c>
-      <c r="U9" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
+      <c r="V9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L10" t="s">
         <v>144</v>
       </c>
-      <c r="K10" t="s">
-        <v>140</v>
-      </c>
-      <c r="L10">
+      <c r="M10">
         <v>12</v>
       </c>
-      <c r="M10">
-        <v>12000</v>
-      </c>
       <c r="N10">
+        <v>1500</v>
+      </c>
+      <c r="O10">
         <v>22000</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>100</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>1</v>
       </c>
-      <c r="Q10" t="s">
-        <v>169</v>
-      </c>
-      <c r="R10">
-        <v>6</v>
-      </c>
-      <c r="S10" s="13">
+      <c r="R10" t="s">
+        <v>173</v>
+      </c>
+      <c r="S10" s="1">
+        <v>57</v>
+      </c>
+      <c r="T10" s="13">
         <v>20</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>100</v>
       </c>
-      <c r="U10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="V10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K11" t="s">
-        <v>140</v>
-      </c>
-      <c r="L11">
+        <v>152</v>
+      </c>
+      <c r="L11" t="s">
+        <v>144</v>
+      </c>
+      <c r="M11">
         <v>12</v>
       </c>
-      <c r="M11">
-        <v>12000</v>
-      </c>
       <c r="N11">
+        <v>1500</v>
+      </c>
+      <c r="O11">
         <v>22000</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>100</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>2</v>
       </c>
-      <c r="Q11" t="s">
-        <v>172</v>
-      </c>
-      <c r="R11">
-        <v>6</v>
-      </c>
-      <c r="S11" s="13">
+      <c r="R11" t="s">
+        <v>176</v>
+      </c>
+      <c r="S11" s="1">
+        <v>58</v>
+      </c>
+      <c r="T11" s="13">
         <v>20</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>100</v>
       </c>
-      <c r="U11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
+      <c r="V11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" t="s">
-        <v>140</v>
-      </c>
-      <c r="L12">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s">
+        <v>144</v>
+      </c>
+      <c r="M12">
         <v>12</v>
       </c>
-      <c r="M12">
-        <v>12000</v>
-      </c>
       <c r="N12">
+        <v>1500</v>
+      </c>
+      <c r="O12">
         <v>22000</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>100</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>2</v>
       </c>
-      <c r="Q12" t="s">
-        <v>175</v>
-      </c>
-      <c r="R12">
-        <v>6</v>
-      </c>
-      <c r="S12" s="13">
+      <c r="R12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S12" s="1">
+        <v>59</v>
+      </c>
+      <c r="T12" s="13">
         <v>20</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>100</v>
       </c>
-      <c r="U12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="15.95" customHeight="1">
+      <c r="V12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="15.95" customHeight="1">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K13" t="s">
-        <v>140</v>
-      </c>
-      <c r="L13">
+        <v>152</v>
+      </c>
+      <c r="L13" t="s">
+        <v>144</v>
+      </c>
+      <c r="M13">
         <v>12</v>
       </c>
-      <c r="M13">
-        <v>20000</v>
-      </c>
       <c r="N13">
+        <v>2400</v>
+      </c>
+      <c r="O13">
         <v>30000</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>150</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>2</v>
       </c>
-      <c r="Q13" t="s">
-        <v>172</v>
-      </c>
-      <c r="R13">
-        <v>6</v>
-      </c>
-      <c r="S13" s="13">
+      <c r="R13" t="s">
+        <v>176</v>
+      </c>
+      <c r="S13" s="1">
+        <v>60</v>
+      </c>
+      <c r="T13" s="13">
         <v>20</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>120</v>
       </c>
-      <c r="U13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
+      <c r="V13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K14" t="s">
-        <v>140</v>
-      </c>
-      <c r="L14">
+        <v>143</v>
+      </c>
+      <c r="L14" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14">
         <v>12</v>
       </c>
-      <c r="M14">
-        <v>20000</v>
-      </c>
       <c r="N14">
+        <v>2400</v>
+      </c>
+      <c r="O14">
         <v>30000</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>150</v>
       </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>182</v>
-      </c>
-      <c r="R14">
-        <v>6</v>
-      </c>
-      <c r="S14" s="13">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>186</v>
+      </c>
+      <c r="S14" s="1">
+        <v>61</v>
+      </c>
+      <c r="T14" s="13">
         <v>20</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>120</v>
       </c>
-      <c r="U14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
+      <c r="V14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L15" t="s">
         <v>144</v>
       </c>
-      <c r="K15" t="s">
-        <v>140</v>
-      </c>
-      <c r="L15">
+      <c r="M15">
         <v>12</v>
       </c>
-      <c r="M15">
-        <v>20000</v>
-      </c>
       <c r="N15">
+        <v>2400</v>
+      </c>
+      <c r="O15">
         <v>30000</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>150</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>1</v>
       </c>
-      <c r="Q15" t="s">
-        <v>186</v>
-      </c>
-      <c r="R15">
-        <v>6</v>
-      </c>
-      <c r="S15" s="13">
+      <c r="R15" t="s">
+        <v>190</v>
+      </c>
+      <c r="S15" s="1">
+        <v>62</v>
+      </c>
+      <c r="T15" s="13">
         <v>20</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>120</v>
       </c>
-      <c r="U15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23">
+      <c r="V15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L16" t="s">
         <v>144</v>
       </c>
-      <c r="K16" t="s">
-        <v>140</v>
-      </c>
-      <c r="L16">
+      <c r="M16">
         <v>12</v>
       </c>
-      <c r="M16">
-        <v>20000</v>
-      </c>
       <c r="N16">
+        <v>2400</v>
+      </c>
+      <c r="O16">
         <v>30000</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>150</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>1</v>
       </c>
-      <c r="Q16" t="s">
-        <v>189</v>
-      </c>
-      <c r="R16">
-        <v>6</v>
-      </c>
-      <c r="S16" s="13">
+      <c r="R16" t="s">
+        <v>193</v>
+      </c>
+      <c r="S16" s="1">
+        <v>63</v>
+      </c>
+      <c r="T16" s="13">
         <v>20</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>120</v>
       </c>
-      <c r="U16" t="s">
-        <v>190</v>
-      </c>
       <c r="V16" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>194</v>
+      </c>
+      <c r="W16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K17" t="s">
+        <v>143</v>
+      </c>
+      <c r="L17" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17">
+        <v>15</v>
+      </c>
+      <c r="N17">
+        <v>4500</v>
+      </c>
+      <c r="O17">
+        <v>50000</v>
+      </c>
+      <c r="P17">
+        <v>200</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>198</v>
+      </c>
+      <c r="S17" s="1">
+        <v>64</v>
+      </c>
+      <c r="T17" s="13">
+        <v>20</v>
+      </c>
+      <c r="U17">
         <v>140</v>
       </c>
-      <c r="L17">
-        <v>15</v>
-      </c>
-      <c r="M17">
-        <v>31000</v>
-      </c>
-      <c r="N17">
-        <v>50000</v>
-      </c>
-      <c r="O17">
-        <v>200</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>194</v>
-      </c>
-      <c r="R17">
-        <v>6</v>
-      </c>
-      <c r="S17" s="13">
-        <v>20</v>
-      </c>
-      <c r="T17">
-        <v>140</v>
-      </c>
-      <c r="U17" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="V17" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L18" t="s">
         <v>144</v>
       </c>
-      <c r="K18" t="s">
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>4500</v>
+      </c>
+      <c r="O18">
+        <v>50000</v>
+      </c>
+      <c r="P18">
+        <v>200</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>202</v>
+      </c>
+      <c r="S18" s="1">
+        <v>65</v>
+      </c>
+      <c r="T18" s="13">
+        <v>20</v>
+      </c>
+      <c r="U18">
         <v>140</v>
       </c>
-      <c r="L18">
-        <v>15</v>
-      </c>
-      <c r="M18">
-        <v>31000</v>
-      </c>
-      <c r="N18">
-        <v>50000</v>
-      </c>
-      <c r="O18">
-        <v>200</v>
-      </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>198</v>
-      </c>
-      <c r="R18">
-        <v>6</v>
-      </c>
-      <c r="S18" s="13">
-        <v>20</v>
-      </c>
-      <c r="T18">
-        <v>140</v>
-      </c>
-      <c r="U18" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="V18" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K19" t="s">
+        <v>152</v>
+      </c>
+      <c r="L19" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>4500</v>
+      </c>
+      <c r="O19">
+        <v>50000</v>
+      </c>
+      <c r="P19">
+        <v>200</v>
+      </c>
+      <c r="Q19">
+        <v>2</v>
+      </c>
+      <c r="R19" t="s">
+        <v>206</v>
+      </c>
+      <c r="S19" s="1">
+        <v>66</v>
+      </c>
+      <c r="T19" s="13">
+        <v>20</v>
+      </c>
+      <c r="U19">
         <v>140</v>
       </c>
-      <c r="L19">
-        <v>15</v>
-      </c>
-      <c r="M19">
-        <v>31000</v>
-      </c>
-      <c r="N19">
-        <v>50000</v>
-      </c>
-      <c r="O19">
-        <v>200</v>
-      </c>
-      <c r="P19">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>202</v>
-      </c>
-      <c r="R19">
-        <v>6</v>
-      </c>
-      <c r="S19" s="13">
-        <v>20</v>
-      </c>
-      <c r="T19">
-        <v>140</v>
-      </c>
-      <c r="U19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="V19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K20" t="s">
+        <v>143</v>
+      </c>
+      <c r="L20" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20">
+        <v>15</v>
+      </c>
+      <c r="N20">
+        <v>4500</v>
+      </c>
+      <c r="O20">
+        <v>50000</v>
+      </c>
+      <c r="P20">
+        <v>200</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>210</v>
+      </c>
+      <c r="S20" s="1">
+        <v>67</v>
+      </c>
+      <c r="T20" s="13">
+        <v>20</v>
+      </c>
+      <c r="U20">
         <v>140</v>
       </c>
-      <c r="L20">
-        <v>15</v>
-      </c>
-      <c r="M20">
-        <v>31000</v>
-      </c>
-      <c r="N20">
-        <v>50000</v>
-      </c>
-      <c r="O20">
-        <v>200</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>206</v>
-      </c>
-      <c r="R20">
-        <v>6</v>
-      </c>
-      <c r="S20" s="13">
-        <v>20</v>
-      </c>
-      <c r="T20">
-        <v>140</v>
-      </c>
-      <c r="U20" t="s">
-        <v>155</v>
-      </c>
       <c r="V20" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>159</v>
+      </c>
+      <c r="W20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I21" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L21" t="s">
         <v>144</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21">
+        <v>15</v>
+      </c>
+      <c r="N21">
+        <v>4500</v>
+      </c>
+      <c r="O21">
+        <v>50000</v>
+      </c>
+      <c r="P21">
+        <v>200</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21" t="s">
+        <v>214</v>
+      </c>
+      <c r="S21" s="1">
+        <v>68</v>
+      </c>
+      <c r="T21" s="13">
+        <v>20</v>
+      </c>
+      <c r="U21">
         <v>140</v>
       </c>
-      <c r="L21">
-        <v>15</v>
-      </c>
-      <c r="M21">
-        <v>31000</v>
-      </c>
-      <c r="N21">
-        <v>50000</v>
-      </c>
-      <c r="O21">
-        <v>200</v>
-      </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>210</v>
-      </c>
-      <c r="R21">
-        <v>6</v>
-      </c>
-      <c r="S21" s="13">
-        <v>20</v>
-      </c>
-      <c r="T21">
-        <v>140</v>
-      </c>
-      <c r="U21" t="s">
-        <v>159</v>
-      </c>
       <c r="V21" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+        <v>163</v>
+      </c>
+      <c r="W21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E22">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K22" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22">
+        <v>15</v>
+      </c>
+      <c r="N22">
+        <v>4500</v>
+      </c>
+      <c r="O22">
+        <v>50000</v>
+      </c>
+      <c r="P22">
+        <v>200</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
+        <v>210</v>
+      </c>
+      <c r="S22" s="1">
+        <v>69</v>
+      </c>
+      <c r="T22" s="13">
+        <v>20</v>
+      </c>
+      <c r="U22">
         <v>140</v>
       </c>
-      <c r="L22">
-        <v>15</v>
-      </c>
-      <c r="M22">
-        <v>31000</v>
-      </c>
-      <c r="N22">
-        <v>50000</v>
-      </c>
-      <c r="O22">
-        <v>200</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>206</v>
-      </c>
-      <c r="R22">
-        <v>6</v>
-      </c>
-      <c r="S22" s="13">
-        <v>20</v>
-      </c>
-      <c r="T22">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C23" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K23" t="s">
+        <v>152</v>
+      </c>
+      <c r="L23" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23">
+        <v>15</v>
+      </c>
+      <c r="N23">
+        <v>4500</v>
+      </c>
+      <c r="O23">
+        <v>50000</v>
+      </c>
+      <c r="P23">
+        <v>200</v>
+      </c>
+      <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23" t="s">
+        <v>220</v>
+      </c>
+      <c r="S23" s="1">
+        <v>70</v>
+      </c>
+      <c r="T23" s="13">
+        <v>20</v>
+      </c>
+      <c r="U23">
         <v>140</v>
       </c>
-      <c r="L23">
-        <v>15</v>
-      </c>
-      <c r="M23">
-        <v>31000</v>
-      </c>
-      <c r="N23">
-        <v>50000</v>
-      </c>
-      <c r="O23">
-        <v>200</v>
-      </c>
-      <c r="P23">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>216</v>
-      </c>
-      <c r="R23">
-        <v>6</v>
-      </c>
-      <c r="S23" s="13">
-        <v>20</v>
-      </c>
-      <c r="T23">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
-      <c r="R24" s="1"/>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="R26" s="1"/>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="R27" s="1"/>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="S24" s="1"/>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="S25" s="1"/>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="S26" s="1"/>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="S27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" customWidth="1"/>
@@ -4338,11 +4426,13 @@
     <col min="7" max="7" width="6.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.85546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="16.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1">
+    <row r="1" spans="1:12" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4356,36 +4446,39 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="30" customHeight="1">
+        <v>477</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>53</v>
@@ -4394,30 +4487,30 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G2" s="1">
         <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1">
+        <v>143</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>53</v>
@@ -4426,30 +4519,30 @@
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G3" s="1">
         <v>6</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1">
+        <v>148</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" customHeight="1">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>53</v>
@@ -4458,472 +4551,472 @@
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G4" s="1">
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1">
+        <v>152</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="33" customHeight="1">
+        <v>237</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="33" customHeight="1">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="K6" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1">
+      <c r="L6" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" customHeight="1">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1">
+        <v>237</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="30" customHeight="1">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" customHeight="1">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" customHeight="1">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" customHeight="1">
+      <c r="L10" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" customHeight="1">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" customHeight="1">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30" customHeight="1">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G13" s="1">
         <v>5</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1">
+        <v>262</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30" customHeight="1">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K14" s="1" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1">
+      <c r="L14" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" customHeight="1">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="42" customHeight="1">
+        <v>270</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="42" customHeight="1">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="30" customHeight="1">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30" customHeight="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30" customHeight="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>53</v>
@@ -4932,30 +5025,30 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G19" s="1">
         <v>9</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" customHeight="1">
+        <v>143</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="30" customHeight="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>53</v>
@@ -4964,30 +5057,30 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="30" customHeight="1">
+        <v>148</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" customHeight="1">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>53</v>
@@ -4996,1662 +5089,1665 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G21" s="1">
         <v>9</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" customHeight="1">
+        <v>152</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="30" customHeight="1">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="30" customHeight="1">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="30" customHeight="1">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="30" customHeight="1">
+        <v>293</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="30" customHeight="1">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="30" customHeight="1">
+        <v>296</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="30" customHeight="1">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="30" customHeight="1">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K27" s="1" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="30" customHeight="1">
+      <c r="L27" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="30" customHeight="1">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="30" customHeight="1">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="30" customHeight="1">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="30" customHeight="1">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="30" customHeight="1">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G32" s="1">
         <v>50</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="30" customHeight="1">
+        <v>270</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="30" customHeight="1">
       <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G33" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="30" customHeight="1">
+        <v>262</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="30" customHeight="1">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G34" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="30" customHeight="1">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G35" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="30" customHeight="1">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G36" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="30" customHeight="1">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="30" customHeight="1">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G38" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="30" customHeight="1">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G39" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="30" customHeight="1">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="30" customHeight="1">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G41" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="30" customHeight="1">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G42" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="30" customHeight="1">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G43" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="30" customHeight="1">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G44" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="30" customHeight="1">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G45" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="30" customHeight="1">
       <c r="A46" s="1">
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G46" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="30" customHeight="1">
       <c r="A47" s="1">
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G47" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="30" customHeight="1">
       <c r="A48" s="1">
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G48" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="30" customHeight="1">
       <c r="A49" s="1">
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G49" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="30" customHeight="1">
+        <v>302</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="30" customHeight="1">
       <c r="A50" s="1">
         <v>48</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G50" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J50" s="1">
         <v>0</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="30" customHeight="1">
+      <c r="L50" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="30" customHeight="1">
       <c r="A51" s="1">
         <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G51" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="30" customHeight="1">
+      <c r="L51" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="30" customHeight="1">
       <c r="A52" s="1">
         <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G52" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J52" s="1">
         <v>0</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="30" customHeight="1">
+      <c r="L52" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="30" customHeight="1">
       <c r="A53" s="1">
         <v>51</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G53" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="30" customHeight="1">
+      <c r="L53" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="30" customHeight="1">
       <c r="A54" s="1">
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>316</v>
+        <v>141</v>
       </c>
       <c r="G54" s="1">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="30" customHeight="1">
+        <v>270</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="165">
       <c r="A55" s="1">
         <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="165">
       <c r="A56" s="1">
         <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="45">
+        <v>249</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="135">
       <c r="A57" s="1">
         <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="135">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="135">
       <c r="A59" s="1">
         <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="135">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="135">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="120">
       <c r="A62" s="1">
         <v>60</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="120">
       <c r="A63" s="1">
         <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="120">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>249</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="120">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="15">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="15">
       <c r="A68" s="1">
         <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="15">
       <c r="A69" s="1">
         <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="D69" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="15">
       <c r="A70" s="1">
         <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="30" customHeight="1">
+    </row>
+    <row r="71" spans="1:12" ht="15">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="30" customHeight="1">
+        <v>249</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="15">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
+        <v>249</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="15"/>
+    <row r="74" spans="1:12" ht="15"/>
+    <row r="75" spans="1:12" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6691,13 +6787,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6705,13 +6801,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6719,13 +6815,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6733,13 +6829,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6747,13 +6843,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D6" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E6" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6761,13 +6857,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D7" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6775,13 +6871,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D8" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6789,13 +6885,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E9" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6803,13 +6899,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E10" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6817,13 +6913,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>451</v>
+      </c>
+      <c r="D11" t="s">
         <v>447</v>
       </c>
-      <c r="D11" t="s">
-        <v>443</v>
-      </c>
       <c r="E11" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -6848,16 +6944,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6865,10 +6961,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6879,10 +6975,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -6893,10 +6989,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -6907,10 +7003,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -6921,10 +7017,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -6935,10 +7031,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -6949,10 +7045,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D8" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -6963,10 +7059,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D9" t="s">
         <v>461</v>
-      </c>
-      <c r="D9" t="s">
-        <v>457</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -6977,10 +7073,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D10" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -6991,10 +7087,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D11" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -7003,4 +7099,72 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2367BEA-D203-4CCB-B0F5-B3733CA3C232}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="K1" t="s">
+        <v>474</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="M1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>